--- a/Mid_Estimate/ER_Summary.xlsx
+++ b/Mid_Estimate/ER_Summary.xlsx
@@ -8,18 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mihirbendre/Documents/Gazelle/Gazelle_2026/Kenya_Project/Agricentric_SOC_Modeling/Mid_Estimate/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D3DA0BA-06D4-A24A-B025-BCAE19BA9FA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3212F7F-2BCF-3741-8A95-C13A828D4509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" xr2:uid="{72AD1D35-862B-EB40-AF7A-21135E5EFD45}"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="6" r:id="rId1"/>
-    <sheet name="Additional_Coop_Projections" sheetId="7" r:id="rId2"/>
-    <sheet name="Eor" sheetId="1" r:id="rId3"/>
-    <sheet name="Lanyuak" sheetId="2" r:id="rId4"/>
-    <sheet name="Mumberes" sheetId="3" r:id="rId5"/>
-    <sheet name="Kabianga" sheetId="4" r:id="rId6"/>
-    <sheet name="Kipsigis" sheetId="5" r:id="rId7"/>
+    <sheet name="Net_Summary" sheetId="9" r:id="rId1"/>
+    <sheet name="Summary_Removals" sheetId="6" r:id="rId2"/>
+    <sheet name="Summary_Reductions" sheetId="8" r:id="rId3"/>
+    <sheet name="Additional_Coop_Projections" sheetId="7" r:id="rId4"/>
+    <sheet name="Eor" sheetId="1" r:id="rId5"/>
+    <sheet name="Lanyuak" sheetId="2" r:id="rId6"/>
+    <sheet name="Mumberes" sheetId="3" r:id="rId7"/>
+    <sheet name="Kabianga" sheetId="4" r:id="rId8"/>
+    <sheet name="Kipsigis" sheetId="5" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,8 +43,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="36">
   <si>
     <t>Maize</t>
   </si>
@@ -117,6 +141,39 @@
   </si>
   <si>
     <t>10yr avg</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Year </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Eor </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Lanyuak </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mumberes </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Kabianga </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Kipsigis </t>
+  </si>
+  <si>
+    <t>Ers (tCO2e/ha/yr)</t>
+  </si>
+  <si>
+    <t>Net Removals</t>
+  </si>
+  <si>
+    <t>Net Reductions</t>
+  </si>
+  <si>
+    <t>Total ERRs</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Net Total Project ERs (QA3) </t>
   </si>
 </sst>
 </file>
@@ -296,6 +353,511 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Net_Summary!$E$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total ERRs</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Net_Summary!$A$3:$A$42</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="40"/>
+                <c:pt idx="0">
+                  <c:v>2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2027</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2028</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2029</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2031</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2032</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2033</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2034</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2036</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2037</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2038</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2039</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2040</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2041</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2042</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2043</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2044</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2045</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2046</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2047</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2048</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2049</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2050</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2051</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2052</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2053</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2054</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2055</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2056</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2057</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2058</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2059</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2060</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2061</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2062</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2063</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2064</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2065</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Net_Summary!$E$3:$E$42</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="40"/>
+                <c:pt idx="0">
+                  <c:v>716897.49590464914</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>384248.20275259414</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>246676.6997447084</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>172685.58126467557</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>131661.66708679614</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>107951.9248329667</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>93438.293158672561</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>83873.728278018927</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>77023.226956977087</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>71704.738765193179</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>67289.518105281881</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>63440.369881515981</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>59974.078186932362</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>56788.960646373293</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>53826.667447029671</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>51052.015083052858</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>48442.327143159942</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>45981.790185254868</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>43658.456717301568</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>41462.646342295448</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>39386.086085778625</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>37421.442083579517</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>35562.058968787285</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>33801.809926236383</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>32135.00610820252</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>30556.338246855328</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>29060.836049714439</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>27643.837702210138</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>26300.965364851781</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>25028.104439431485</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>23821.385380107185</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>22677.167358414223</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>21592.023376887737</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>20562.72658056856</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>19586.237600336495</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>18659.692809936241</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>17780.393406313353</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>16945.795240031057</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>16153.4993337696</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>15401.24303464601</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F1CC-8447-9B56-B6FD5BCE0FAD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1755631023"/>
+        <c:axId val="1756241087"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1755631023"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1756241087"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1756241087"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1755631023"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
       <c:tx>
         <c:rich>
           <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
@@ -366,7 +928,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Summary!$B$5</c:f>
+              <c:f>Summary_Removals!$B$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -389,7 +951,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Summary!$A$6:$A$45</c:f>
+              <c:f>Summary_Removals!$A$6:$A$45</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="40"/>
@@ -518,7 +1080,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Summary!$B$6:$B$45</c:f>
+              <c:f>Summary_Removals!$B$6:$B$45</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="40"/>
@@ -657,7 +1219,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Summary!$C$5</c:f>
+              <c:f>Summary_Removals!$C$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -680,7 +1242,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Summary!$A$6:$A$45</c:f>
+              <c:f>Summary_Removals!$A$6:$A$45</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="40"/>
@@ -809,7 +1371,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Summary!$C$6:$C$45</c:f>
+              <c:f>Summary_Removals!$C$6:$C$45</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="40"/>
@@ -948,7 +1510,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Summary!$D$5</c:f>
+              <c:f>Summary_Removals!$D$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -971,7 +1533,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Summary!$A$6:$A$45</c:f>
+              <c:f>Summary_Removals!$A$6:$A$45</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="40"/>
@@ -1100,7 +1662,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Summary!$D$6:$D$45</c:f>
+              <c:f>Summary_Removals!$D$6:$D$45</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="40"/>
@@ -1239,7 +1801,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Summary!$E$5</c:f>
+              <c:f>Summary_Removals!$E$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1262,7 +1824,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Summary!$A$6:$A$45</c:f>
+              <c:f>Summary_Removals!$A$6:$A$45</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="40"/>
@@ -1391,7 +1953,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Summary!$E$6:$E$45</c:f>
+              <c:f>Summary_Removals!$E$6:$E$45</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="40"/>
@@ -1530,7 +2092,7 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Summary!$F$5</c:f>
+              <c:f>Summary_Removals!$F$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1553,7 +2115,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Summary!$A$6:$A$45</c:f>
+              <c:f>Summary_Removals!$A$6:$A$45</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="40"/>
@@ -1682,7 +2244,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Summary!$F$6:$F$45</c:f>
+              <c:f>Summary_Removals!$F$6:$F$45</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="40"/>
@@ -2011,7 +2573,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -2066,7 +2628,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Summary!$H$5</c:f>
+              <c:f>Summary_Removals!$H$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2101,7 +2663,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$A$6:$A$45</c:f>
+              <c:f>Summary_Removals!$A$6:$A$45</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="40"/>
@@ -2230,7 +2792,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$H$6:$H$45</c:f>
+              <c:f>Summary_Removals!$H$6:$H$45</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="40"/>
@@ -2544,7 +3106,540 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Summary_Reductions!$H$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>  Net Total Project ERs (QA3)  </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Summary_Reductions!$A$8:$A$47</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="40"/>
+                <c:pt idx="0">
+                  <c:v>2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2027</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2028</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2029</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2031</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2032</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2033</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2034</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2036</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2037</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2038</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2039</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2040</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2041</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2042</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2043</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2044</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2045</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2046</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2047</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2048</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2049</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2050</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2051</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2052</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2053</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2054</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2055</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2056</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2057</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2058</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2059</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2060</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2061</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2062</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2063</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2064</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2065</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Summary_Reductions!$H$8:$H$47</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="40"/>
+                <c:pt idx="0">
+                  <c:v>442.435</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>442.435</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>442.435</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>442.435</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>442.435</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>442.435</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>442.435</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>442.435</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>442.435</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>442.435</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>442.435</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>442.435</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>442.435</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>442.435</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>442.435</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>442.435</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>442.435</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>442.435</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>442.435</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>442.435</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>442.435</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>442.435</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>442.435</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>442.435</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>442.435</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>442.435</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>442.435</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>442.435</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>442.435</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>442.435</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>442.435</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>442.435</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>442.435</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>442.435</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>442.435</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>442.435</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>442.435</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>442.435</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>442.435</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>442.435</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4E18-F046-91FB-9CD4AC8B51A6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="750822943"/>
+        <c:axId val="1773808671"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="750822943"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1773808671"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1773808671"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="750822943"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -3066,6 +4161,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
@@ -3583,7 +4758,7 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -3610,8 +4785,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -3691,6 +4866,11 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -3701,6 +4881,11 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
@@ -3712,7 +4897,7 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="19050" cap="rnd">
+      <a:ln w="28575" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -3732,6 +4917,9 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3744,10 +4932,10 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -3787,23 +4975,22 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -3908,8 +5095,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -4041,20 +5228,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -4068,17 +5254,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -4099,7 +5274,7 @@
 </file>
 
 <file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -4126,8 +5301,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -4207,6 +5382,1038 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="phClr"/>
@@ -4615,6 +6822,47 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>454393</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>77551</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>85649</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>180217</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C65423D-C7CD-1788-7CEB-C21C4B63D7BA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -4691,7 +6939,48 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>406041</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>68330</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>41140</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>137375</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{528B6CC6-B4FD-E787-58F8-B8AE0622F8D0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -5048,6 +7337,677 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53C74460-226A-484F-A8DD-FFF53BF916A1}">
+  <dimension ref="A2:E42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="2" max="2" width="14.1640625" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>2026</v>
+      </c>
+      <c r="B3" s="1" cm="1">
+        <f t="array" ref="B3:B42">Summary_Removals!H6:H45</f>
+        <v>716455.06090464909</v>
+      </c>
+      <c r="C3">
+        <f>Summary_Reductions!H8</f>
+        <v>442.435</v>
+      </c>
+      <c r="E3" s="6">
+        <f>SUM(B3:C3)</f>
+        <v>716897.49590464914</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>2027</v>
+      </c>
+      <c r="B4" s="1">
+        <v>383805.76775259414</v>
+      </c>
+      <c r="C4">
+        <f>Summary_Reductions!H9</f>
+        <v>442.435</v>
+      </c>
+      <c r="E4" s="6">
+        <f t="shared" ref="E4:E42" si="0">SUM(B4:C4)</f>
+        <v>384248.20275259414</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5">
+        <v>2028</v>
+      </c>
+      <c r="B5" s="1">
+        <v>246234.2647447084</v>
+      </c>
+      <c r="C5">
+        <f>Summary_Reductions!H10</f>
+        <v>442.435</v>
+      </c>
+      <c r="E5" s="6">
+        <f t="shared" si="0"/>
+        <v>246676.6997447084</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6">
+        <v>2029</v>
+      </c>
+      <c r="B6" s="1">
+        <v>172243.14626467557</v>
+      </c>
+      <c r="C6">
+        <f>Summary_Reductions!H11</f>
+        <v>442.435</v>
+      </c>
+      <c r="E6" s="6">
+        <f t="shared" si="0"/>
+        <v>172685.58126467557</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7">
+        <v>2030</v>
+      </c>
+      <c r="B7" s="1">
+        <v>131219.23208679614</v>
+      </c>
+      <c r="C7">
+        <f>Summary_Reductions!H12</f>
+        <v>442.435</v>
+      </c>
+      <c r="E7" s="6">
+        <f t="shared" si="0"/>
+        <v>131661.66708679614</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8">
+        <v>2031</v>
+      </c>
+      <c r="B8" s="1">
+        <v>107509.4898329667</v>
+      </c>
+      <c r="C8">
+        <f>Summary_Reductions!H13</f>
+        <v>442.435</v>
+      </c>
+      <c r="E8" s="6">
+        <f t="shared" si="0"/>
+        <v>107951.9248329667</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9">
+        <v>2032</v>
+      </c>
+      <c r="B9" s="1">
+        <v>92995.858158672563</v>
+      </c>
+      <c r="C9">
+        <f>Summary_Reductions!H14</f>
+        <v>442.435</v>
+      </c>
+      <c r="E9" s="6">
+        <f t="shared" si="0"/>
+        <v>93438.293158672561</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10">
+        <v>2033</v>
+      </c>
+      <c r="B10" s="1">
+        <v>83431.293278018929</v>
+      </c>
+      <c r="C10">
+        <f>Summary_Reductions!H15</f>
+        <v>442.435</v>
+      </c>
+      <c r="E10" s="6">
+        <f t="shared" si="0"/>
+        <v>83873.728278018927</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11">
+        <v>2034</v>
+      </c>
+      <c r="B11" s="1">
+        <v>76580.791956977089</v>
+      </c>
+      <c r="C11">
+        <f>Summary_Reductions!H16</f>
+        <v>442.435</v>
+      </c>
+      <c r="E11" s="6">
+        <f t="shared" si="0"/>
+        <v>77023.226956977087</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12">
+        <v>2035</v>
+      </c>
+      <c r="B12" s="1">
+        <v>71262.303765193181</v>
+      </c>
+      <c r="C12">
+        <f>Summary_Reductions!H17</f>
+        <v>442.435</v>
+      </c>
+      <c r="E12" s="6">
+        <f t="shared" si="0"/>
+        <v>71704.738765193179</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13">
+        <v>2036</v>
+      </c>
+      <c r="B13" s="1">
+        <v>66847.083105281883</v>
+      </c>
+      <c r="C13">
+        <f>Summary_Reductions!H18</f>
+        <v>442.435</v>
+      </c>
+      <c r="E13" s="6">
+        <f t="shared" si="0"/>
+        <v>67289.518105281881</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14">
+        <v>2037</v>
+      </c>
+      <c r="B14" s="1">
+        <v>62997.934881515983</v>
+      </c>
+      <c r="C14">
+        <f>Summary_Reductions!H19</f>
+        <v>442.435</v>
+      </c>
+      <c r="E14" s="6">
+        <f>SUM(B14:C14)</f>
+        <v>63440.369881515981</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15">
+        <v>2038</v>
+      </c>
+      <c r="B15" s="1">
+        <v>59531.643186932364</v>
+      </c>
+      <c r="C15">
+        <f>Summary_Reductions!H20</f>
+        <v>442.435</v>
+      </c>
+      <c r="E15" s="6">
+        <f t="shared" si="0"/>
+        <v>59974.078186932362</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16">
+        <v>2039</v>
+      </c>
+      <c r="B16" s="1">
+        <v>56346.525646373295</v>
+      </c>
+      <c r="C16">
+        <f>Summary_Reductions!H21</f>
+        <v>442.435</v>
+      </c>
+      <c r="E16" s="6">
+        <f t="shared" si="0"/>
+        <v>56788.960646373293</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>2040</v>
+      </c>
+      <c r="B17" s="1">
+        <v>53384.232447029673</v>
+      </c>
+      <c r="C17">
+        <f>Summary_Reductions!H22</f>
+        <v>442.435</v>
+      </c>
+      <c r="E17" s="6">
+        <f t="shared" si="0"/>
+        <v>53826.667447029671</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>2041</v>
+      </c>
+      <c r="B18" s="1">
+        <v>50609.580083052861</v>
+      </c>
+      <c r="C18">
+        <f>Summary_Reductions!H23</f>
+        <v>442.435</v>
+      </c>
+      <c r="E18" s="6">
+        <f t="shared" si="0"/>
+        <v>51052.015083052858</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>2042</v>
+      </c>
+      <c r="B19" s="1">
+        <v>47999.892143159945</v>
+      </c>
+      <c r="C19">
+        <f>Summary_Reductions!H24</f>
+        <v>442.435</v>
+      </c>
+      <c r="E19" s="6">
+        <f t="shared" si="0"/>
+        <v>48442.327143159942</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>2043</v>
+      </c>
+      <c r="B20" s="1">
+        <v>45539.35518525487</v>
+      </c>
+      <c r="C20">
+        <f>Summary_Reductions!H25</f>
+        <v>442.435</v>
+      </c>
+      <c r="E20" s="6">
+        <f t="shared" si="0"/>
+        <v>45981.790185254868</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>2044</v>
+      </c>
+      <c r="B21" s="1">
+        <v>43216.02171730157</v>
+      </c>
+      <c r="C21">
+        <f>Summary_Reductions!H26</f>
+        <v>442.435</v>
+      </c>
+      <c r="E21" s="6">
+        <f t="shared" si="0"/>
+        <v>43658.456717301568</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>2045</v>
+      </c>
+      <c r="B22" s="1">
+        <v>41020.21134229545</v>
+      </c>
+      <c r="C22">
+        <f>Summary_Reductions!H27</f>
+        <v>442.435</v>
+      </c>
+      <c r="E22" s="6">
+        <f t="shared" si="0"/>
+        <v>41462.646342295448</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>2046</v>
+      </c>
+      <c r="B23" s="1">
+        <v>38943.651085778627</v>
+      </c>
+      <c r="C23">
+        <f>Summary_Reductions!H28</f>
+        <v>442.435</v>
+      </c>
+      <c r="E23" s="6">
+        <f t="shared" si="0"/>
+        <v>39386.086085778625</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>2047</v>
+      </c>
+      <c r="B24" s="1">
+        <v>36979.00708357952</v>
+      </c>
+      <c r="C24">
+        <f>Summary_Reductions!H29</f>
+        <v>442.435</v>
+      </c>
+      <c r="E24" s="6">
+        <f t="shared" si="0"/>
+        <v>37421.442083579517</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>2048</v>
+      </c>
+      <c r="B25" s="1">
+        <v>35119.623968787288</v>
+      </c>
+      <c r="C25">
+        <f>Summary_Reductions!H30</f>
+        <v>442.435</v>
+      </c>
+      <c r="E25" s="6">
+        <f t="shared" si="0"/>
+        <v>35562.058968787285</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>2049</v>
+      </c>
+      <c r="B26" s="1">
+        <v>33359.374926236385</v>
+      </c>
+      <c r="C26">
+        <f>Summary_Reductions!H31</f>
+        <v>442.435</v>
+      </c>
+      <c r="E26" s="6">
+        <f t="shared" si="0"/>
+        <v>33801.809926236383</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>2050</v>
+      </c>
+      <c r="B27" s="1">
+        <v>31692.571108202519</v>
+      </c>
+      <c r="C27">
+        <f>Summary_Reductions!H32</f>
+        <v>442.435</v>
+      </c>
+      <c r="E27" s="6">
+        <f t="shared" si="0"/>
+        <v>32135.00610820252</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
+        <v>2051</v>
+      </c>
+      <c r="B28" s="1">
+        <v>30113.903246855327</v>
+      </c>
+      <c r="C28">
+        <f>Summary_Reductions!H33</f>
+        <v>442.435</v>
+      </c>
+      <c r="E28" s="6">
+        <f t="shared" si="0"/>
+        <v>30556.338246855328</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29">
+        <v>2052</v>
+      </c>
+      <c r="B29" s="1">
+        <v>28618.401049714437</v>
+      </c>
+      <c r="C29">
+        <f>Summary_Reductions!H34</f>
+        <v>442.435</v>
+      </c>
+      <c r="E29" s="6">
+        <f t="shared" si="0"/>
+        <v>29060.836049714439</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30">
+        <v>2053</v>
+      </c>
+      <c r="B30" s="1">
+        <v>27201.402702210136</v>
+      </c>
+      <c r="C30">
+        <f>Summary_Reductions!H35</f>
+        <v>442.435</v>
+      </c>
+      <c r="E30" s="6">
+        <f t="shared" si="0"/>
+        <v>27643.837702210138</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31">
+        <v>2054</v>
+      </c>
+      <c r="B31" s="1">
+        <v>25858.53036485178</v>
+      </c>
+      <c r="C31">
+        <f>Summary_Reductions!H36</f>
+        <v>442.435</v>
+      </c>
+      <c r="E31" s="6">
+        <f t="shared" si="0"/>
+        <v>26300.965364851781</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32">
+        <v>2055</v>
+      </c>
+      <c r="B32" s="1">
+        <v>24585.669439431484</v>
+      </c>
+      <c r="C32">
+        <f>Summary_Reductions!H37</f>
+        <v>442.435</v>
+      </c>
+      <c r="E32" s="6">
+        <f t="shared" si="0"/>
+        <v>25028.104439431485</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33">
+        <v>2056</v>
+      </c>
+      <c r="B33" s="1">
+        <v>23378.950380107184</v>
+      </c>
+      <c r="C33">
+        <f>Summary_Reductions!H38</f>
+        <v>442.435</v>
+      </c>
+      <c r="E33" s="6">
+        <f t="shared" si="0"/>
+        <v>23821.385380107185</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34">
+        <v>2057</v>
+      </c>
+      <c r="B34" s="1">
+        <v>22234.732358414221</v>
+      </c>
+      <c r="C34">
+        <f>Summary_Reductions!H39</f>
+        <v>442.435</v>
+      </c>
+      <c r="E34" s="6">
+        <f t="shared" si="0"/>
+        <v>22677.167358414223</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35">
+        <v>2058</v>
+      </c>
+      <c r="B35" s="1">
+        <v>21149.588376887736</v>
+      </c>
+      <c r="C35">
+        <f>Summary_Reductions!H40</f>
+        <v>442.435</v>
+      </c>
+      <c r="E35" s="6">
+        <f t="shared" si="0"/>
+        <v>21592.023376887737</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36">
+        <v>2059</v>
+      </c>
+      <c r="B36" s="1">
+        <v>20120.291580568559</v>
+      </c>
+      <c r="C36">
+        <f>Summary_Reductions!H41</f>
+        <v>442.435</v>
+      </c>
+      <c r="E36" s="6">
+        <f t="shared" si="0"/>
+        <v>20562.72658056856</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37">
+        <v>2060</v>
+      </c>
+      <c r="B37" s="1">
+        <v>19143.802600336494</v>
+      </c>
+      <c r="C37">
+        <f>Summary_Reductions!H42</f>
+        <v>442.435</v>
+      </c>
+      <c r="E37" s="6">
+        <f t="shared" si="0"/>
+        <v>19586.237600336495</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38">
+        <v>2061</v>
+      </c>
+      <c r="B38" s="1">
+        <v>18217.25780993624</v>
+      </c>
+      <c r="C38">
+        <f>Summary_Reductions!H43</f>
+        <v>442.435</v>
+      </c>
+      <c r="E38" s="6">
+        <f t="shared" si="0"/>
+        <v>18659.692809936241</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39">
+        <v>2062</v>
+      </c>
+      <c r="B39" s="1">
+        <v>17337.958406313352</v>
+      </c>
+      <c r="C39">
+        <f>Summary_Reductions!H44</f>
+        <v>442.435</v>
+      </c>
+      <c r="E39" s="6">
+        <f t="shared" si="0"/>
+        <v>17780.393406313353</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40">
+        <v>2063</v>
+      </c>
+      <c r="B40" s="1">
+        <v>16503.360240031056</v>
+      </c>
+      <c r="C40">
+        <f>Summary_Reductions!H45</f>
+        <v>442.435</v>
+      </c>
+      <c r="E40" s="6">
+        <f t="shared" si="0"/>
+        <v>16945.795240031057</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41">
+        <v>2064</v>
+      </c>
+      <c r="B41" s="1">
+        <v>15711.0643337696</v>
+      </c>
+      <c r="C41">
+        <f>Summary_Reductions!H46</f>
+        <v>442.435</v>
+      </c>
+      <c r="E41" s="6">
+        <f t="shared" si="0"/>
+        <v>16153.4993337696</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42">
+        <v>2065</v>
+      </c>
+      <c r="B42" s="1">
+        <v>14958.80803464601</v>
+      </c>
+      <c r="C42">
+        <f>Summary_Reductions!H47</f>
+        <v>442.435</v>
+      </c>
+      <c r="E42" s="6">
+        <f t="shared" si="0"/>
+        <v>15401.24303464601</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3DABBA3-596E-B946-9E4A-D51BBBAF87D8}">
   <dimension ref="A3:H50"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -6284,7 +9244,1251 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8796C41C-1BC9-EA45-B875-C5F0B93D7AE5}">
+  <dimension ref="A2:H47"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="16.5" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2">
+        <v>4387</v>
+      </c>
+      <c r="C2">
+        <v>4636</v>
+      </c>
+      <c r="D2">
+        <v>1310</v>
+      </c>
+      <c r="E2">
+        <v>15358</v>
+      </c>
+      <c r="F2">
+        <v>9678</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3">
+        <v>0.03</v>
+      </c>
+      <c r="C3">
+        <v>0.1</v>
+      </c>
+      <c r="D3">
+        <v>0.03</v>
+      </c>
+      <c r="E3">
+        <v>0.01</v>
+      </c>
+      <c r="F3">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8">
+        <v>2026</v>
+      </c>
+      <c r="B8">
+        <f>B$3*B$2</f>
+        <v>131.60999999999999</v>
+      </c>
+      <c r="C8">
+        <f t="shared" ref="C8:F23" si="0">C$3*C$2</f>
+        <v>463.6</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>39.299999999999997</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>153.58000000000001</v>
+      </c>
+      <c r="F8">
+        <f>F$3*F$2</f>
+        <v>96.78</v>
+      </c>
+      <c r="H8">
+        <f>SUM(B8:F8) * 0.5</f>
+        <v>442.435</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9">
+        <v>2027</v>
+      </c>
+      <c r="B9">
+        <f t="shared" ref="B9:F24" si="1">B$3*B$2</f>
+        <v>131.60999999999999</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="0"/>
+        <v>463.6</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>39.299999999999997</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="0"/>
+        <v>153.58000000000001</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>96.78</v>
+      </c>
+      <c r="H9">
+        <f t="shared" ref="H9:H47" si="2">SUM(B9:F9) * 0.5</f>
+        <v>442.435</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10">
+        <v>2028</v>
+      </c>
+      <c r="B10">
+        <f t="shared" si="1"/>
+        <v>131.60999999999999</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="0"/>
+        <v>463.6</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="0"/>
+        <v>39.299999999999997</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="0"/>
+        <v>153.58000000000001</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="0"/>
+        <v>96.78</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="2"/>
+        <v>442.435</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11">
+        <v>2029</v>
+      </c>
+      <c r="B11">
+        <f t="shared" si="1"/>
+        <v>131.60999999999999</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="0"/>
+        <v>463.6</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="0"/>
+        <v>39.299999999999997</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="0"/>
+        <v>153.58000000000001</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>96.78</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="2"/>
+        <v>442.435</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12">
+        <v>2030</v>
+      </c>
+      <c r="B12">
+        <f t="shared" si="1"/>
+        <v>131.60999999999999</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="0"/>
+        <v>463.6</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="0"/>
+        <v>39.299999999999997</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="0"/>
+        <v>153.58000000000001</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="0"/>
+        <v>96.78</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="2"/>
+        <v>442.435</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13">
+        <v>2031</v>
+      </c>
+      <c r="B13">
+        <f t="shared" si="1"/>
+        <v>131.60999999999999</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="0"/>
+        <v>463.6</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="0"/>
+        <v>39.299999999999997</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="0"/>
+        <v>153.58000000000001</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="0"/>
+        <v>96.78</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="2"/>
+        <v>442.435</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14">
+        <v>2032</v>
+      </c>
+      <c r="B14">
+        <f t="shared" si="1"/>
+        <v>131.60999999999999</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="0"/>
+        <v>463.6</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="0"/>
+        <v>39.299999999999997</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="0"/>
+        <v>153.58000000000001</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="0"/>
+        <v>96.78</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="2"/>
+        <v>442.435</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15">
+        <v>2033</v>
+      </c>
+      <c r="B15">
+        <f t="shared" si="1"/>
+        <v>131.60999999999999</v>
+      </c>
+      <c r="C15">
+        <f t="shared" si="0"/>
+        <v>463.6</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="0"/>
+        <v>39.299999999999997</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="0"/>
+        <v>153.58000000000001</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="0"/>
+        <v>96.78</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="2"/>
+        <v>442.435</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16">
+        <v>2034</v>
+      </c>
+      <c r="B16">
+        <f t="shared" si="1"/>
+        <v>131.60999999999999</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="0"/>
+        <v>463.6</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="0"/>
+        <v>39.299999999999997</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="0"/>
+        <v>153.58000000000001</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="0"/>
+        <v>96.78</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="2"/>
+        <v>442.435</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17">
+        <v>2035</v>
+      </c>
+      <c r="B17">
+        <f t="shared" si="1"/>
+        <v>131.60999999999999</v>
+      </c>
+      <c r="C17">
+        <f t="shared" si="0"/>
+        <v>463.6</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="0"/>
+        <v>39.299999999999997</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="0"/>
+        <v>153.58000000000001</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="0"/>
+        <v>96.78</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="2"/>
+        <v>442.435</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18">
+        <v>2036</v>
+      </c>
+      <c r="B18">
+        <f t="shared" si="1"/>
+        <v>131.60999999999999</v>
+      </c>
+      <c r="C18">
+        <f t="shared" si="0"/>
+        <v>463.6</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="0"/>
+        <v>39.299999999999997</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="0"/>
+        <v>153.58000000000001</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="0"/>
+        <v>96.78</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="2"/>
+        <v>442.435</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19">
+        <v>2037</v>
+      </c>
+      <c r="B19">
+        <f t="shared" si="1"/>
+        <v>131.60999999999999</v>
+      </c>
+      <c r="C19">
+        <f t="shared" si="0"/>
+        <v>463.6</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="0"/>
+        <v>39.299999999999997</v>
+      </c>
+      <c r="E19">
+        <f t="shared" si="0"/>
+        <v>153.58000000000001</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="0"/>
+        <v>96.78</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="2"/>
+        <v>442.435</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20">
+        <v>2038</v>
+      </c>
+      <c r="B20">
+        <f t="shared" si="1"/>
+        <v>131.60999999999999</v>
+      </c>
+      <c r="C20">
+        <f t="shared" si="0"/>
+        <v>463.6</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="0"/>
+        <v>39.299999999999997</v>
+      </c>
+      <c r="E20">
+        <f t="shared" si="0"/>
+        <v>153.58000000000001</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="0"/>
+        <v>96.78</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="2"/>
+        <v>442.435</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21">
+        <v>2039</v>
+      </c>
+      <c r="B21">
+        <f t="shared" si="1"/>
+        <v>131.60999999999999</v>
+      </c>
+      <c r="C21">
+        <f t="shared" si="0"/>
+        <v>463.6</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="0"/>
+        <v>39.299999999999997</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="0"/>
+        <v>153.58000000000001</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="0"/>
+        <v>96.78</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="2"/>
+        <v>442.435</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22">
+        <v>2040</v>
+      </c>
+      <c r="B22">
+        <f t="shared" si="1"/>
+        <v>131.60999999999999</v>
+      </c>
+      <c r="C22">
+        <f t="shared" si="0"/>
+        <v>463.6</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="0"/>
+        <v>39.299999999999997</v>
+      </c>
+      <c r="E22">
+        <f t="shared" si="0"/>
+        <v>153.58000000000001</v>
+      </c>
+      <c r="F22">
+        <f t="shared" si="0"/>
+        <v>96.78</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="2"/>
+        <v>442.435</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23">
+        <v>2041</v>
+      </c>
+      <c r="B23">
+        <f t="shared" si="1"/>
+        <v>131.60999999999999</v>
+      </c>
+      <c r="C23">
+        <f t="shared" si="0"/>
+        <v>463.6</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="0"/>
+        <v>39.299999999999997</v>
+      </c>
+      <c r="E23">
+        <f t="shared" si="0"/>
+        <v>153.58000000000001</v>
+      </c>
+      <c r="F23">
+        <f t="shared" si="0"/>
+        <v>96.78</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="2"/>
+        <v>442.435</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24">
+        <v>2042</v>
+      </c>
+      <c r="B24">
+        <f t="shared" si="1"/>
+        <v>131.60999999999999</v>
+      </c>
+      <c r="C24">
+        <f t="shared" si="1"/>
+        <v>463.6</v>
+      </c>
+      <c r="D24">
+        <f t="shared" si="1"/>
+        <v>39.299999999999997</v>
+      </c>
+      <c r="E24">
+        <f t="shared" si="1"/>
+        <v>153.58000000000001</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="1"/>
+        <v>96.78</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="2"/>
+        <v>442.435</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25">
+        <v>2043</v>
+      </c>
+      <c r="B25">
+        <f t="shared" ref="B25:F47" si="3">B$3*B$2</f>
+        <v>131.60999999999999</v>
+      </c>
+      <c r="C25">
+        <f t="shared" si="3"/>
+        <v>463.6</v>
+      </c>
+      <c r="D25">
+        <f t="shared" si="3"/>
+        <v>39.299999999999997</v>
+      </c>
+      <c r="E25">
+        <f t="shared" si="3"/>
+        <v>153.58000000000001</v>
+      </c>
+      <c r="F25">
+        <f t="shared" si="3"/>
+        <v>96.78</v>
+      </c>
+      <c r="H25">
+        <f t="shared" si="2"/>
+        <v>442.435</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26">
+        <v>2044</v>
+      </c>
+      <c r="B26">
+        <f t="shared" si="3"/>
+        <v>131.60999999999999</v>
+      </c>
+      <c r="C26">
+        <f t="shared" si="3"/>
+        <v>463.6</v>
+      </c>
+      <c r="D26">
+        <f t="shared" si="3"/>
+        <v>39.299999999999997</v>
+      </c>
+      <c r="E26">
+        <f t="shared" si="3"/>
+        <v>153.58000000000001</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="3"/>
+        <v>96.78</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="2"/>
+        <v>442.435</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27">
+        <v>2045</v>
+      </c>
+      <c r="B27">
+        <f t="shared" si="3"/>
+        <v>131.60999999999999</v>
+      </c>
+      <c r="C27">
+        <f t="shared" si="3"/>
+        <v>463.6</v>
+      </c>
+      <c r="D27">
+        <f t="shared" si="3"/>
+        <v>39.299999999999997</v>
+      </c>
+      <c r="E27">
+        <f t="shared" si="3"/>
+        <v>153.58000000000001</v>
+      </c>
+      <c r="F27">
+        <f t="shared" si="3"/>
+        <v>96.78</v>
+      </c>
+      <c r="H27">
+        <f t="shared" si="2"/>
+        <v>442.435</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28">
+        <v>2046</v>
+      </c>
+      <c r="B28">
+        <f t="shared" si="3"/>
+        <v>131.60999999999999</v>
+      </c>
+      <c r="C28">
+        <f t="shared" si="3"/>
+        <v>463.6</v>
+      </c>
+      <c r="D28">
+        <f t="shared" si="3"/>
+        <v>39.299999999999997</v>
+      </c>
+      <c r="E28">
+        <f t="shared" si="3"/>
+        <v>153.58000000000001</v>
+      </c>
+      <c r="F28">
+        <f t="shared" si="3"/>
+        <v>96.78</v>
+      </c>
+      <c r="H28">
+        <f t="shared" si="2"/>
+        <v>442.435</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29">
+        <v>2047</v>
+      </c>
+      <c r="B29">
+        <f t="shared" si="3"/>
+        <v>131.60999999999999</v>
+      </c>
+      <c r="C29">
+        <f t="shared" si="3"/>
+        <v>463.6</v>
+      </c>
+      <c r="D29">
+        <f t="shared" si="3"/>
+        <v>39.299999999999997</v>
+      </c>
+      <c r="E29">
+        <f t="shared" si="3"/>
+        <v>153.58000000000001</v>
+      </c>
+      <c r="F29">
+        <f t="shared" si="3"/>
+        <v>96.78</v>
+      </c>
+      <c r="H29">
+        <f t="shared" si="2"/>
+        <v>442.435</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30">
+        <v>2048</v>
+      </c>
+      <c r="B30">
+        <f t="shared" si="3"/>
+        <v>131.60999999999999</v>
+      </c>
+      <c r="C30">
+        <f t="shared" si="3"/>
+        <v>463.6</v>
+      </c>
+      <c r="D30">
+        <f t="shared" si="3"/>
+        <v>39.299999999999997</v>
+      </c>
+      <c r="E30">
+        <f t="shared" si="3"/>
+        <v>153.58000000000001</v>
+      </c>
+      <c r="F30">
+        <f t="shared" si="3"/>
+        <v>96.78</v>
+      </c>
+      <c r="H30">
+        <f t="shared" si="2"/>
+        <v>442.435</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31">
+        <v>2049</v>
+      </c>
+      <c r="B31">
+        <f t="shared" si="3"/>
+        <v>131.60999999999999</v>
+      </c>
+      <c r="C31">
+        <f t="shared" si="3"/>
+        <v>463.6</v>
+      </c>
+      <c r="D31">
+        <f t="shared" si="3"/>
+        <v>39.299999999999997</v>
+      </c>
+      <c r="E31">
+        <f t="shared" si="3"/>
+        <v>153.58000000000001</v>
+      </c>
+      <c r="F31">
+        <f t="shared" si="3"/>
+        <v>96.78</v>
+      </c>
+      <c r="H31">
+        <f t="shared" si="2"/>
+        <v>442.435</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32">
+        <v>2050</v>
+      </c>
+      <c r="B32">
+        <f t="shared" si="3"/>
+        <v>131.60999999999999</v>
+      </c>
+      <c r="C32">
+        <f t="shared" si="3"/>
+        <v>463.6</v>
+      </c>
+      <c r="D32">
+        <f t="shared" si="3"/>
+        <v>39.299999999999997</v>
+      </c>
+      <c r="E32">
+        <f t="shared" si="3"/>
+        <v>153.58000000000001</v>
+      </c>
+      <c r="F32">
+        <f t="shared" si="3"/>
+        <v>96.78</v>
+      </c>
+      <c r="H32">
+        <f t="shared" si="2"/>
+        <v>442.435</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33">
+        <v>2051</v>
+      </c>
+      <c r="B33">
+        <f t="shared" si="3"/>
+        <v>131.60999999999999</v>
+      </c>
+      <c r="C33">
+        <f t="shared" si="3"/>
+        <v>463.6</v>
+      </c>
+      <c r="D33">
+        <f t="shared" si="3"/>
+        <v>39.299999999999997</v>
+      </c>
+      <c r="E33">
+        <f t="shared" si="3"/>
+        <v>153.58000000000001</v>
+      </c>
+      <c r="F33">
+        <f t="shared" si="3"/>
+        <v>96.78</v>
+      </c>
+      <c r="H33">
+        <f t="shared" si="2"/>
+        <v>442.435</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34">
+        <v>2052</v>
+      </c>
+      <c r="B34">
+        <f t="shared" si="3"/>
+        <v>131.60999999999999</v>
+      </c>
+      <c r="C34">
+        <f t="shared" si="3"/>
+        <v>463.6</v>
+      </c>
+      <c r="D34">
+        <f t="shared" si="3"/>
+        <v>39.299999999999997</v>
+      </c>
+      <c r="E34">
+        <f t="shared" si="3"/>
+        <v>153.58000000000001</v>
+      </c>
+      <c r="F34">
+        <f t="shared" si="3"/>
+        <v>96.78</v>
+      </c>
+      <c r="H34">
+        <f t="shared" si="2"/>
+        <v>442.435</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35">
+        <v>2053</v>
+      </c>
+      <c r="B35">
+        <f t="shared" si="3"/>
+        <v>131.60999999999999</v>
+      </c>
+      <c r="C35">
+        <f t="shared" si="3"/>
+        <v>463.6</v>
+      </c>
+      <c r="D35">
+        <f t="shared" si="3"/>
+        <v>39.299999999999997</v>
+      </c>
+      <c r="E35">
+        <f t="shared" si="3"/>
+        <v>153.58000000000001</v>
+      </c>
+      <c r="F35">
+        <f t="shared" si="3"/>
+        <v>96.78</v>
+      </c>
+      <c r="H35">
+        <f t="shared" si="2"/>
+        <v>442.435</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36">
+        <v>2054</v>
+      </c>
+      <c r="B36">
+        <f t="shared" si="3"/>
+        <v>131.60999999999999</v>
+      </c>
+      <c r="C36">
+        <f t="shared" si="3"/>
+        <v>463.6</v>
+      </c>
+      <c r="D36">
+        <f t="shared" si="3"/>
+        <v>39.299999999999997</v>
+      </c>
+      <c r="E36">
+        <f t="shared" si="3"/>
+        <v>153.58000000000001</v>
+      </c>
+      <c r="F36">
+        <f t="shared" si="3"/>
+        <v>96.78</v>
+      </c>
+      <c r="H36">
+        <f t="shared" si="2"/>
+        <v>442.435</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37">
+        <v>2055</v>
+      </c>
+      <c r="B37">
+        <f t="shared" si="3"/>
+        <v>131.60999999999999</v>
+      </c>
+      <c r="C37">
+        <f t="shared" si="3"/>
+        <v>463.6</v>
+      </c>
+      <c r="D37">
+        <f t="shared" si="3"/>
+        <v>39.299999999999997</v>
+      </c>
+      <c r="E37">
+        <f t="shared" si="3"/>
+        <v>153.58000000000001</v>
+      </c>
+      <c r="F37">
+        <f t="shared" si="3"/>
+        <v>96.78</v>
+      </c>
+      <c r="H37">
+        <f t="shared" si="2"/>
+        <v>442.435</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38">
+        <v>2056</v>
+      </c>
+      <c r="B38">
+        <f t="shared" si="3"/>
+        <v>131.60999999999999</v>
+      </c>
+      <c r="C38">
+        <f t="shared" si="3"/>
+        <v>463.6</v>
+      </c>
+      <c r="D38">
+        <f t="shared" si="3"/>
+        <v>39.299999999999997</v>
+      </c>
+      <c r="E38">
+        <f t="shared" si="3"/>
+        <v>153.58000000000001</v>
+      </c>
+      <c r="F38">
+        <f t="shared" si="3"/>
+        <v>96.78</v>
+      </c>
+      <c r="H38">
+        <f t="shared" si="2"/>
+        <v>442.435</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39">
+        <v>2057</v>
+      </c>
+      <c r="B39">
+        <f t="shared" si="3"/>
+        <v>131.60999999999999</v>
+      </c>
+      <c r="C39">
+        <f t="shared" si="3"/>
+        <v>463.6</v>
+      </c>
+      <c r="D39">
+        <f t="shared" si="3"/>
+        <v>39.299999999999997</v>
+      </c>
+      <c r="E39">
+        <f t="shared" si="3"/>
+        <v>153.58000000000001</v>
+      </c>
+      <c r="F39">
+        <f t="shared" si="3"/>
+        <v>96.78</v>
+      </c>
+      <c r="H39">
+        <f t="shared" si="2"/>
+        <v>442.435</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40">
+        <v>2058</v>
+      </c>
+      <c r="B40">
+        <f t="shared" si="3"/>
+        <v>131.60999999999999</v>
+      </c>
+      <c r="C40">
+        <f t="shared" si="3"/>
+        <v>463.6</v>
+      </c>
+      <c r="D40">
+        <f t="shared" si="3"/>
+        <v>39.299999999999997</v>
+      </c>
+      <c r="E40">
+        <f t="shared" si="3"/>
+        <v>153.58000000000001</v>
+      </c>
+      <c r="F40">
+        <f t="shared" si="3"/>
+        <v>96.78</v>
+      </c>
+      <c r="H40">
+        <f t="shared" si="2"/>
+        <v>442.435</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41">
+        <v>2059</v>
+      </c>
+      <c r="B41">
+        <f t="shared" si="3"/>
+        <v>131.60999999999999</v>
+      </c>
+      <c r="C41">
+        <f t="shared" si="3"/>
+        <v>463.6</v>
+      </c>
+      <c r="D41">
+        <f t="shared" si="3"/>
+        <v>39.299999999999997</v>
+      </c>
+      <c r="E41">
+        <f t="shared" si="3"/>
+        <v>153.58000000000001</v>
+      </c>
+      <c r="F41">
+        <f t="shared" si="3"/>
+        <v>96.78</v>
+      </c>
+      <c r="H41">
+        <f t="shared" si="2"/>
+        <v>442.435</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42">
+        <v>2060</v>
+      </c>
+      <c r="B42">
+        <f t="shared" si="3"/>
+        <v>131.60999999999999</v>
+      </c>
+      <c r="C42">
+        <f t="shared" si="3"/>
+        <v>463.6</v>
+      </c>
+      <c r="D42">
+        <f t="shared" si="3"/>
+        <v>39.299999999999997</v>
+      </c>
+      <c r="E42">
+        <f t="shared" si="3"/>
+        <v>153.58000000000001</v>
+      </c>
+      <c r="F42">
+        <f t="shared" si="3"/>
+        <v>96.78</v>
+      </c>
+      <c r="H42">
+        <f t="shared" si="2"/>
+        <v>442.435</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43">
+        <v>2061</v>
+      </c>
+      <c r="B43">
+        <f t="shared" si="3"/>
+        <v>131.60999999999999</v>
+      </c>
+      <c r="C43">
+        <f t="shared" si="3"/>
+        <v>463.6</v>
+      </c>
+      <c r="D43">
+        <f t="shared" si="3"/>
+        <v>39.299999999999997</v>
+      </c>
+      <c r="E43">
+        <f t="shared" si="3"/>
+        <v>153.58000000000001</v>
+      </c>
+      <c r="F43">
+        <f t="shared" si="3"/>
+        <v>96.78</v>
+      </c>
+      <c r="H43">
+        <f t="shared" si="2"/>
+        <v>442.435</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44">
+        <v>2062</v>
+      </c>
+      <c r="B44">
+        <f t="shared" si="3"/>
+        <v>131.60999999999999</v>
+      </c>
+      <c r="C44">
+        <f t="shared" si="3"/>
+        <v>463.6</v>
+      </c>
+      <c r="D44">
+        <f t="shared" si="3"/>
+        <v>39.299999999999997</v>
+      </c>
+      <c r="E44">
+        <f t="shared" si="3"/>
+        <v>153.58000000000001</v>
+      </c>
+      <c r="F44">
+        <f t="shared" si="3"/>
+        <v>96.78</v>
+      </c>
+      <c r="H44">
+        <f t="shared" si="2"/>
+        <v>442.435</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45">
+        <v>2063</v>
+      </c>
+      <c r="B45">
+        <f t="shared" si="3"/>
+        <v>131.60999999999999</v>
+      </c>
+      <c r="C45">
+        <f t="shared" si="3"/>
+        <v>463.6</v>
+      </c>
+      <c r="D45">
+        <f t="shared" si="3"/>
+        <v>39.299999999999997</v>
+      </c>
+      <c r="E45">
+        <f t="shared" si="3"/>
+        <v>153.58000000000001</v>
+      </c>
+      <c r="F45">
+        <f t="shared" si="3"/>
+        <v>96.78</v>
+      </c>
+      <c r="H45">
+        <f t="shared" si="2"/>
+        <v>442.435</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46">
+        <v>2064</v>
+      </c>
+      <c r="B46">
+        <f t="shared" si="3"/>
+        <v>131.60999999999999</v>
+      </c>
+      <c r="C46">
+        <f t="shared" si="3"/>
+        <v>463.6</v>
+      </c>
+      <c r="D46">
+        <f t="shared" si="3"/>
+        <v>39.299999999999997</v>
+      </c>
+      <c r="E46">
+        <f t="shared" si="3"/>
+        <v>153.58000000000001</v>
+      </c>
+      <c r="F46">
+        <f t="shared" si="3"/>
+        <v>96.78</v>
+      </c>
+      <c r="H46">
+        <f t="shared" si="2"/>
+        <v>442.435</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47">
+        <v>2065</v>
+      </c>
+      <c r="B47">
+        <f t="shared" si="3"/>
+        <v>131.60999999999999</v>
+      </c>
+      <c r="C47">
+        <f t="shared" si="3"/>
+        <v>463.6</v>
+      </c>
+      <c r="D47">
+        <f t="shared" si="3"/>
+        <v>39.299999999999997</v>
+      </c>
+      <c r="E47">
+        <f t="shared" si="3"/>
+        <v>153.58000000000001</v>
+      </c>
+      <c r="F47">
+        <f t="shared" si="3"/>
+        <v>96.78</v>
+      </c>
+      <c r="H47">
+        <f t="shared" si="2"/>
+        <v>442.435</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9AB2BFC-0ECB-3141-9EA5-B06B472A45A9}">
   <dimension ref="A1:L51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="15.33203125" defaultRowHeight="16"/>
@@ -6340,7 +10544,7 @@
         <v>2026</v>
       </c>
       <c r="B3" s="1">
-        <f>Summary!$H6</f>
+        <f>Summary_Removals!$H6</f>
         <v>716455.06090464909</v>
       </c>
       <c r="L3" s="6">
@@ -6353,11 +10557,11 @@
         <v>2027</v>
       </c>
       <c r="B4" s="1">
-        <f>Summary!$H7</f>
+        <f>Summary_Removals!$H7</f>
         <v>383805.76775259414</v>
       </c>
       <c r="C4" s="1">
-        <f>Summary!$H6</f>
+        <f>Summary_Removals!$H6</f>
         <v>716455.06090464909</v>
       </c>
       <c r="L4" s="6">
@@ -6370,15 +10574,15 @@
         <v>2028</v>
       </c>
       <c r="B5" s="1">
-        <f>Summary!$H8</f>
+        <f>Summary_Removals!$H8</f>
         <v>246234.2647447084</v>
       </c>
       <c r="C5" s="1">
-        <f>Summary!$H7</f>
+        <f>Summary_Removals!$H7</f>
         <v>383805.76775259414</v>
       </c>
       <c r="D5" s="7">
-        <f>Summary!$H6</f>
+        <f>Summary_Removals!$H6</f>
         <v>716455.06090464909</v>
       </c>
       <c r="L5" s="6">
@@ -6391,19 +10595,19 @@
         <v>2029</v>
       </c>
       <c r="B6" s="1">
-        <f>Summary!$H9</f>
+        <f>Summary_Removals!$H9</f>
         <v>172243.14626467557</v>
       </c>
       <c r="C6" s="1">
-        <f>Summary!$H8</f>
+        <f>Summary_Removals!$H8</f>
         <v>246234.2647447084</v>
       </c>
       <c r="D6" s="7">
-        <f>Summary!$H7</f>
+        <f>Summary_Removals!$H7</f>
         <v>383805.76775259414</v>
       </c>
       <c r="E6" s="7">
-        <f>Summary!$H6</f>
+        <f>Summary_Removals!$H6</f>
         <v>716455.06090464909</v>
       </c>
       <c r="L6" s="6">
@@ -6416,23 +10620,23 @@
         <v>2030</v>
       </c>
       <c r="B7" s="1">
-        <f>Summary!$H10</f>
+        <f>Summary_Removals!$H10</f>
         <v>131219.23208679614</v>
       </c>
       <c r="C7" s="1">
-        <f>Summary!$H9</f>
+        <f>Summary_Removals!$H9</f>
         <v>172243.14626467557</v>
       </c>
       <c r="D7" s="7">
-        <f>Summary!$H8</f>
+        <f>Summary_Removals!$H8</f>
         <v>246234.2647447084</v>
       </c>
       <c r="E7" s="7">
-        <f>Summary!$H7</f>
+        <f>Summary_Removals!$H7</f>
         <v>383805.76775259414</v>
       </c>
       <c r="F7" s="7">
-        <f>Summary!$H6</f>
+        <f>Summary_Removals!$H6</f>
         <v>716455.06090464909</v>
       </c>
       <c r="L7" s="6">
@@ -6445,27 +10649,27 @@
         <v>2031</v>
       </c>
       <c r="B8" s="1">
-        <f>Summary!$H11</f>
+        <f>Summary_Removals!$H11</f>
         <v>107509.4898329667</v>
       </c>
       <c r="C8" s="1">
-        <f>Summary!$H10</f>
+        <f>Summary_Removals!$H10</f>
         <v>131219.23208679614</v>
       </c>
       <c r="D8" s="7">
-        <f>Summary!$H9</f>
+        <f>Summary_Removals!$H9</f>
         <v>172243.14626467557</v>
       </c>
       <c r="E8" s="7">
-        <f>Summary!$H8</f>
+        <f>Summary_Removals!$H8</f>
         <v>246234.2647447084</v>
       </c>
       <c r="F8" s="7">
-        <f>Summary!$H7</f>
+        <f>Summary_Removals!$H7</f>
         <v>383805.76775259414</v>
       </c>
       <c r="G8" s="7">
-        <f>Summary!$H6</f>
+        <f>Summary_Removals!$H6</f>
         <v>716455.06090464909</v>
       </c>
       <c r="L8" s="6">
@@ -6478,31 +10682,31 @@
         <v>2032</v>
       </c>
       <c r="B9" s="1">
-        <f>Summary!$H12</f>
+        <f>Summary_Removals!$H12</f>
         <v>92995.858158672563</v>
       </c>
       <c r="C9" s="1">
-        <f>Summary!$H11</f>
+        <f>Summary_Removals!$H11</f>
         <v>107509.4898329667</v>
       </c>
       <c r="D9" s="7">
-        <f>Summary!$H10</f>
+        <f>Summary_Removals!$H10</f>
         <v>131219.23208679614</v>
       </c>
       <c r="E9" s="7">
-        <f>Summary!$H9</f>
+        <f>Summary_Removals!$H9</f>
         <v>172243.14626467557</v>
       </c>
       <c r="F9" s="7">
-        <f>Summary!$H8</f>
+        <f>Summary_Removals!$H8</f>
         <v>246234.2647447084</v>
       </c>
       <c r="G9" s="7">
-        <f>Summary!$H7</f>
+        <f>Summary_Removals!$H7</f>
         <v>383805.76775259414</v>
       </c>
       <c r="H9" s="7">
-        <f>Summary!$H6</f>
+        <f>Summary_Removals!$H6</f>
         <v>716455.06090464909</v>
       </c>
       <c r="L9" s="6">
@@ -6515,35 +10719,35 @@
         <v>2033</v>
       </c>
       <c r="B10" s="1">
-        <f>Summary!$H13</f>
+        <f>Summary_Removals!$H13</f>
         <v>83431.293278018929</v>
       </c>
       <c r="C10" s="1">
-        <f>Summary!$H12</f>
+        <f>Summary_Removals!$H12</f>
         <v>92995.858158672563</v>
       </c>
       <c r="D10" s="7">
-        <f>Summary!$H11</f>
+        <f>Summary_Removals!$H11</f>
         <v>107509.4898329667</v>
       </c>
       <c r="E10" s="7">
-        <f>Summary!$H10</f>
+        <f>Summary_Removals!$H10</f>
         <v>131219.23208679614</v>
       </c>
       <c r="F10" s="7">
-        <f>Summary!$H9</f>
+        <f>Summary_Removals!$H9</f>
         <v>172243.14626467557</v>
       </c>
       <c r="G10" s="7">
-        <f>Summary!$H8</f>
+        <f>Summary_Removals!$H8</f>
         <v>246234.2647447084</v>
       </c>
       <c r="H10" s="7">
-        <f>Summary!$H7</f>
+        <f>Summary_Removals!$H7</f>
         <v>383805.76775259414</v>
       </c>
       <c r="I10" s="7">
-        <f>Summary!$H6</f>
+        <f>Summary_Removals!$H6</f>
         <v>716455.06090464909</v>
       </c>
       <c r="L10" s="6">
@@ -6556,39 +10760,39 @@
         <v>2034</v>
       </c>
       <c r="B11" s="1">
-        <f>Summary!$H14</f>
+        <f>Summary_Removals!$H14</f>
         <v>76580.791956977089</v>
       </c>
       <c r="C11" s="1">
-        <f>Summary!$H13</f>
+        <f>Summary_Removals!$H13</f>
         <v>83431.293278018929</v>
       </c>
       <c r="D11" s="7">
-        <f>Summary!$H12</f>
+        <f>Summary_Removals!$H12</f>
         <v>92995.858158672563</v>
       </c>
       <c r="E11" s="7">
-        <f>Summary!$H11</f>
+        <f>Summary_Removals!$H11</f>
         <v>107509.4898329667</v>
       </c>
       <c r="F11" s="7">
-        <f>Summary!$H10</f>
+        <f>Summary_Removals!$H10</f>
         <v>131219.23208679614</v>
       </c>
       <c r="G11" s="7">
-        <f>Summary!$H9</f>
+        <f>Summary_Removals!$H9</f>
         <v>172243.14626467557</v>
       </c>
       <c r="H11" s="7">
-        <f>Summary!$H8</f>
+        <f>Summary_Removals!$H8</f>
         <v>246234.2647447084</v>
       </c>
       <c r="I11" s="7">
-        <f>Summary!$H7</f>
+        <f>Summary_Removals!$H7</f>
         <v>383805.76775259414</v>
       </c>
       <c r="J11" s="7">
-        <f>Summary!$H6</f>
+        <f>Summary_Removals!$H6</f>
         <v>716455.06090464909</v>
       </c>
       <c r="L11" s="6">
@@ -6601,43 +10805,43 @@
         <v>2035</v>
       </c>
       <c r="B12" s="1">
-        <f>Summary!$H15</f>
+        <f>Summary_Removals!$H15</f>
         <v>71262.303765193181</v>
       </c>
       <c r="C12" s="1">
-        <f>Summary!$H14</f>
+        <f>Summary_Removals!$H14</f>
         <v>76580.791956977089</v>
       </c>
       <c r="D12" s="7">
-        <f>Summary!$H13</f>
+        <f>Summary_Removals!$H13</f>
         <v>83431.293278018929</v>
       </c>
       <c r="E12" s="7">
-        <f>Summary!$H12</f>
+        <f>Summary_Removals!$H12</f>
         <v>92995.858158672563</v>
       </c>
       <c r="F12" s="7">
-        <f>Summary!$H11</f>
+        <f>Summary_Removals!$H11</f>
         <v>107509.4898329667</v>
       </c>
       <c r="G12" s="7">
-        <f>Summary!$H10</f>
+        <f>Summary_Removals!$H10</f>
         <v>131219.23208679614</v>
       </c>
       <c r="H12" s="7">
-        <f>Summary!$H9</f>
+        <f>Summary_Removals!$H9</f>
         <v>172243.14626467557</v>
       </c>
       <c r="I12" s="7">
-        <f>Summary!$H8</f>
+        <f>Summary_Removals!$H8</f>
         <v>246234.2647447084</v>
       </c>
       <c r="J12" s="7">
-        <f>Summary!$H7</f>
+        <f>Summary_Removals!$H7</f>
         <v>383805.76775259414</v>
       </c>
       <c r="K12" s="7">
-        <f>Summary!$H6</f>
+        <f>Summary_Removals!$H6</f>
         <v>716455.06090464909</v>
       </c>
       <c r="L12" s="6">
@@ -7088,7 +11292,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F4CAE5B-3D09-7B43-B8F9-21D8EE6819FF}">
   <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -7604,7 +11808,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4CF8AA5-7D0F-844D-A4B9-F3670363D091}">
   <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -8366,7 +12570,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA3A5171-09C2-EF45-9A29-949687B747C9}">
   <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -8471,6 +12675,13 @@
         <f t="shared" si="0"/>
         <v>24701.847530589963</v>
       </c>
+      <c r="G5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="1">
+        <f>SUM(H3:H4)</f>
+        <v>1310.27</v>
+      </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6">
@@ -9148,7 +13359,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A50DF0E0-E6D0-CC4C-B19B-7767FC3863D6}">
   <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -9664,7 +13875,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{736FD4D8-5019-BD44-95E6-DECAB01CDB7E}">
   <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>

--- a/Mid_Estimate/ER_Summary.xlsx
+++ b/Mid_Estimate/ER_Summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mihirbendre/Documents/Gazelle/Gazelle_2026/Kenya_Project/Agricentric_SOC_Modeling/Mid_Estimate/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3212F7F-2BCF-3741-8A95-C13A828D4509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A7784B4-595D-3E45-B4D9-EC1F4E828CFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" xr2:uid="{72AD1D35-862B-EB40-AF7A-21135E5EFD45}"/>
   </bookViews>
@@ -7338,7 +7338,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53C74460-226A-484F-A8DD-FFF53BF916A1}">
-  <dimension ref="A2:E42"/>
+  <dimension ref="A2:E44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="14.1640625" customWidth="1"/>
@@ -7999,6 +7999,12 @@
       <c r="E42" s="6">
         <f t="shared" si="0"/>
         <v>15401.24303464601</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="E44" s="6">
+        <f>SUM(E3:E42)</f>
+        <v>3128155.0375801069</v>
       </c>
     </row>
   </sheetData>

--- a/Mid_Estimate/ER_Summary.xlsx
+++ b/Mid_Estimate/ER_Summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mihirbendre/Documents/Gazelle/Gazelle_2026/Kenya_Project/Agricentric_SOC_Modeling/Mid_Estimate/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A7784B4-595D-3E45-B4D9-EC1F4E828CFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D247D3F7-C2E3-4A46-AF88-127165FADBB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" xr2:uid="{72AD1D35-862B-EB40-AF7A-21135E5EFD45}"/>
+    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" activeTab="3" xr2:uid="{72AD1D35-862B-EB40-AF7A-21135E5EFD45}"/>
   </bookViews>
   <sheets>
     <sheet name="Net_Summary" sheetId="9" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="40">
   <si>
     <t>Maize</t>
   </si>
@@ -174,6 +174,18 @@
   </si>
   <si>
     <t xml:space="preserve"> Net Total Project ERs (QA3) </t>
+  </si>
+  <si>
+    <t>Total (1st 10y)</t>
+  </si>
+  <si>
+    <t>Avg/yr (1st 10y)</t>
+  </si>
+  <si>
+    <t>Total (40y)</t>
+  </si>
+  <si>
+    <t>Avg/yr (40y)</t>
   </si>
 </sst>
 </file>
@@ -3674,11 +3686,19 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>ERs/yr,</a:t>
+              <a:t>40y</a:t>
             </a:r>
             <a:r>
               <a:rPr lang="en-US" baseline="0"/>
-              <a:t> w/ +5 coops/yr</a:t>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>ERs,</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> w/ +5 coops/y during 1st 10y</a:t>
             </a:r>
             <a:r>
               <a:rPr lang="en-US"/>
@@ -3695,26 +3715,6 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -3723,8 +3723,279 @@
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="0"/>
+          <c:idx val="2"/>
           <c:order val="0"/>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Additional_Coop_Projections!$A$3:$A$42</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="40"/>
+                <c:pt idx="0">
+                  <c:v>2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2027</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2028</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2029</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2031</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2032</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2033</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2034</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2036</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2037</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2038</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2039</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2040</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2041</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2042</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2043</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2044</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2045</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2046</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2047</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2048</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2049</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2050</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2051</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2052</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2053</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2054</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2055</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2056</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2057</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2058</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2059</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2060</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2061</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2062</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2063</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2064</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2065</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Additional_Coop_Projections!$L$3:$L$42</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="40"/>
+                <c:pt idx="0">
+                  <c:v>716455.06090464909</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1100260.8286572432</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1346495.0934019517</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1518738.2396666273</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1649957.4717534233</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1757466.9615863902</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1850462.8197450626</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1933894.1130230816</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2010474.9049800585</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2081737.2087452519</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1432129.2309458847</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1111321.3980748064</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>924618.77651703032</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>808722.15589872818</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>730887.15625896165</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>673987.24650904781</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>628991.28049353522</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>591099.3424007711</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>557734.57216109557</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>527492.47973819787</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>499589.04771869461</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>473570.11992075818</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>449158.10070261307</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>426170.94998247619</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>404479.28864364902</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>383983.61180745147</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>364602.12071400601</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>346264.16823096125</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>328906.67687851144</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>312472.13497564744</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>296907.43426997605</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>282163.15954481077</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>268193.12395291124</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>254954.04060724337</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>242405.27209937741</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>230508.62666245832</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>219228.1840190572</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>208530.14155687811</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>198382.67552579593</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>188755.81412101045</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-9A6A-E149-BCC4-1A569F9E18DE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="1"/>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
@@ -3739,10 +4010,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Additional_Coop_Projections!$A$3:$A$12</c:f>
+              <c:f>Additional_Coop_Projections!$A$3:$A$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="40"/>
                 <c:pt idx="0">
                   <c:v>2026</c:v>
                 </c:pt>
@@ -3772,16 +4043,106 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2036</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2037</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2038</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2039</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2040</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2041</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2042</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2043</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2044</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2045</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2046</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2047</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2048</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2049</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2050</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2051</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2052</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2053</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2054</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2055</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2056</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2057</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2058</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2059</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2060</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2061</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2062</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2063</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2064</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2065</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Additional_Coop_Projections!$L$3:$L$12</c:f>
+              <c:f>Additional_Coop_Projections!$L$3:$L$42</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="40"/>
                 <c:pt idx="0">
                   <c:v>716455.06090464909</c:v>
                 </c:pt>
@@ -3811,6 +4172,96 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>2081737.2087452519</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1432129.2309458847</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1111321.3980748064</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>924618.77651703032</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>808722.15589872818</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>730887.15625896165</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>673987.24650904781</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>628991.28049353522</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>591099.3424007711</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>557734.57216109557</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>527492.47973819787</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>499589.04771869461</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>473570.11992075818</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>449158.10070261307</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>426170.94998247619</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>404479.28864364902</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>383983.61180745147</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>364602.12071400601</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>346264.16823096125</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>328906.67687851144</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>312472.13497564744</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>296907.43426997605</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>282163.15954481077</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>268193.12395291124</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>254954.04060724337</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>242405.27209937741</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>230508.62666245832</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>219228.1840190572</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>208530.14155687811</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>198382.67552579593</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>188755.81412101045</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3818,7 +4269,558 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-5771-2C42-9E44-63BC99E67322}"/>
+              <c16:uniqueId val="{00000008-9A6A-E149-BCC4-1A569F9E18DE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="2"/>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Additional_Coop_Projections!$A$3:$A$42</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="40"/>
+                <c:pt idx="0">
+                  <c:v>2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2027</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2028</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2029</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2031</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2032</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2033</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2034</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2036</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2037</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2038</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2039</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2040</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2041</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2042</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2043</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2044</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2045</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2046</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2047</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2048</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2049</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2050</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2051</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2052</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2053</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2054</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2055</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2056</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2057</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2058</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2059</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2060</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2061</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2062</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2063</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2064</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2065</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Additional_Coop_Projections!$L$3:$L$42</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="40"/>
+                <c:pt idx="0">
+                  <c:v>716455.06090464909</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1100260.8286572432</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1346495.0934019517</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1518738.2396666273</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1649957.4717534233</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1757466.9615863902</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1850462.8197450626</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1933894.1130230816</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2010474.9049800585</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2081737.2087452519</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1432129.2309458847</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1111321.3980748064</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>924618.77651703032</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>808722.15589872818</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>730887.15625896165</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>673987.24650904781</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>628991.28049353522</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>591099.3424007711</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>557734.57216109557</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>527492.47973819787</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>499589.04771869461</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>473570.11992075818</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>449158.10070261307</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>426170.94998247619</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>404479.28864364902</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>383983.61180745147</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>364602.12071400601</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>346264.16823096125</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>328906.67687851144</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>312472.13497564744</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>296907.43426997605</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>282163.15954481077</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>268193.12395291124</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>254954.04060724337</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>242405.27209937741</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>230508.62666245832</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>219228.1840190572</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>208530.14155687811</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>198382.67552579593</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>188755.81412101045</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-9A6A-E149-BCC4-1A569F9E18DE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="3"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Additional_Coop_Projections!$A$3:$A$42</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="40"/>
+                <c:pt idx="0">
+                  <c:v>2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2027</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2028</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2029</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2031</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2032</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2033</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2034</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2036</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2037</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2038</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2039</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2040</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2041</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2042</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2043</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2044</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2045</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2046</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2047</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2048</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2049</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2050</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2051</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2052</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2053</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2054</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2055</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2056</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2057</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2058</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2059</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2060</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2061</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2062</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2063</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2064</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2065</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Additional_Coop_Projections!$L$3:$L$42</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="40"/>
+                <c:pt idx="0">
+                  <c:v>716455.06090464909</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1100260.8286572432</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1346495.0934019517</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1518738.2396666273</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1649957.4717534233</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1757466.9615863902</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1850462.8197450626</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1933894.1130230816</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2010474.9049800585</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2081737.2087452519</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1432129.2309458847</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1111321.3980748064</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>924618.77651703032</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>808722.15589872818</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>730887.15625896165</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>673987.24650904781</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>628991.28049353522</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>591099.3424007711</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>557734.57216109557</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>527492.47973819787</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>499589.04771869461</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>473570.11992075818</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>449158.10070261307</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>426170.94998247619</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>404479.28864364902</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>383983.61180745147</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>364602.12071400601</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>346264.16823096125</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>328906.67687851144</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>312472.13497564744</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>296907.43426997605</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>282163.15954481077</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>268193.12395291124</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>254954.04060724337</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>242405.27209937741</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>230508.62666245832</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>219228.1840190572</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>208530.14155687811</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>198382.67552579593</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>188755.81412101045</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-9A6A-E149-BCC4-1A569F9E18DE}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3940,26 +4942,6 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
         </c:title>
         <c:numFmt formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -3996,33 +4978,11 @@
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
   </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
   <c:txPr>
     <a:bodyPr/>
     <a:lstStyle/>
@@ -4162,46 +5122,6 @@
 </file>
 
 <file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -6305,522 +7225,6 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -6984,16 +7388,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>1021080</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>5080</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>489865</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>51835</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>919480</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>106680</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>388265</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>158238</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -10571,7 +10975,7 @@
         <v>716455.06090464909</v>
       </c>
       <c r="L4" s="6">
-        <f t="shared" ref="L4:L12" si="0">SUM(B4:K4)</f>
+        <f t="shared" ref="L4:L42" si="0">SUM(B4:K4)</f>
         <v>1100260.8286572432</v>
       </c>
     </row>
@@ -10856,378 +11260,1480 @@
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="B13" s="1"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
+      <c r="A13">
+        <v>2036</v>
+      </c>
+      <c r="B13" s="1">
+        <f>Summary_Removals!$H16</f>
+        <v>66847.083105281883</v>
+      </c>
+      <c r="C13" s="1">
+        <f>Summary_Removals!$H15</f>
+        <v>71262.303765193181</v>
+      </c>
+      <c r="D13" s="7">
+        <f>Summary_Removals!$H14</f>
+        <v>76580.791956977089</v>
+      </c>
+      <c r="E13" s="7">
+        <f>Summary_Removals!$H13</f>
+        <v>83431.293278018929</v>
+      </c>
+      <c r="F13" s="7">
+        <f>Summary_Removals!$H12</f>
+        <v>92995.858158672563</v>
+      </c>
+      <c r="G13" s="7">
+        <f>Summary_Removals!$H11</f>
+        <v>107509.4898329667</v>
+      </c>
+      <c r="H13" s="7">
+        <f>Summary_Removals!$H10</f>
+        <v>131219.23208679614</v>
+      </c>
+      <c r="I13" s="7">
+        <f>Summary_Removals!$H9</f>
+        <v>172243.14626467557</v>
+      </c>
+      <c r="J13" s="7">
+        <f>Summary_Removals!$H8</f>
+        <v>246234.2647447084</v>
+      </c>
+      <c r="K13" s="7">
+        <f>Summary_Removals!$H7</f>
+        <v>383805.76775259414</v>
+      </c>
+      <c r="L13" s="6">
+        <f>SUM(B13:K13)</f>
+        <v>1432129.2309458847</v>
+      </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" t="s">
-        <v>21</v>
+      <c r="A14">
+        <v>2037</v>
       </c>
       <c r="B14" s="1">
-        <f>SUM(B3:K12)</f>
-        <v>15965942.702463739</v>
-      </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
+        <f>Summary_Removals!$H17</f>
+        <v>62997.934881515983</v>
+      </c>
+      <c r="C14" s="1">
+        <f>Summary_Removals!$H16</f>
+        <v>66847.083105281883</v>
+      </c>
+      <c r="D14" s="7">
+        <f>Summary_Removals!$H15</f>
+        <v>71262.303765193181</v>
+      </c>
+      <c r="E14" s="7">
+        <f>Summary_Removals!$H14</f>
+        <v>76580.791956977089</v>
+      </c>
+      <c r="F14" s="7">
+        <f>Summary_Removals!$H13</f>
+        <v>83431.293278018929</v>
+      </c>
+      <c r="G14" s="7">
+        <f>Summary_Removals!$H12</f>
+        <v>92995.858158672563</v>
+      </c>
+      <c r="H14" s="7">
+        <f>Summary_Removals!$H11</f>
+        <v>107509.4898329667</v>
+      </c>
+      <c r="I14" s="7">
+        <f>Summary_Removals!$H10</f>
+        <v>131219.23208679614</v>
+      </c>
+      <c r="J14" s="7">
+        <f>Summary_Removals!$H9</f>
+        <v>172243.14626467557</v>
+      </c>
+      <c r="K14" s="7">
+        <f>Summary_Removals!$H8</f>
+        <v>246234.2647447084</v>
+      </c>
+      <c r="L14" s="6">
+        <f t="shared" si="0"/>
+        <v>1111321.3980748064</v>
+      </c>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" t="s">
-        <v>20</v>
+      <c r="A15">
+        <v>2038</v>
       </c>
       <c r="B15" s="1">
-        <f>B14/10</f>
-        <v>1596594.270246374</v>
-      </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
+        <f>Summary_Removals!$H18</f>
+        <v>59531.643186932364</v>
+      </c>
+      <c r="C15" s="1">
+        <f>Summary_Removals!$H17</f>
+        <v>62997.934881515983</v>
+      </c>
+      <c r="D15" s="7">
+        <f>Summary_Removals!$H16</f>
+        <v>66847.083105281883</v>
+      </c>
+      <c r="E15" s="7">
+        <f>Summary_Removals!$H15</f>
+        <v>71262.303765193181</v>
+      </c>
+      <c r="F15" s="7">
+        <f>Summary_Removals!$H14</f>
+        <v>76580.791956977089</v>
+      </c>
+      <c r="G15" s="7">
+        <f>Summary_Removals!$H13</f>
+        <v>83431.293278018929</v>
+      </c>
+      <c r="H15" s="7">
+        <f>Summary_Removals!$H12</f>
+        <v>92995.858158672563</v>
+      </c>
+      <c r="I15" s="7">
+        <f>Summary_Removals!$H11</f>
+        <v>107509.4898329667</v>
+      </c>
+      <c r="J15" s="7">
+        <f>Summary_Removals!$H10</f>
+        <v>131219.23208679614</v>
+      </c>
+      <c r="K15" s="7">
+        <f>Summary_Removals!$H9</f>
+        <v>172243.14626467557</v>
+      </c>
+      <c r="L15" s="6">
+        <f>SUM(B15:K15)</f>
+        <v>924618.77651703032</v>
+      </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="B16" s="1"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-    </row>
-    <row r="17" spans="2:11">
-      <c r="B17" s="1"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-    </row>
-    <row r="18" spans="2:11">
-      <c r="B18" s="1"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-    </row>
-    <row r="19" spans="2:11">
-      <c r="B19" s="1"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
-    </row>
-    <row r="20" spans="2:11">
-      <c r="B20" s="1"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-    </row>
-    <row r="21" spans="2:11">
-      <c r="B21" s="1"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-    </row>
-    <row r="22" spans="2:11">
-      <c r="B22" s="1"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-    </row>
-    <row r="23" spans="2:11">
-      <c r="B23" s="1"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-    </row>
-    <row r="24" spans="2:11">
-      <c r="B24" s="1"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-    </row>
-    <row r="25" spans="2:11">
-      <c r="B25" s="1"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-    </row>
-    <row r="26" spans="2:11">
-      <c r="B26" s="1"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-    </row>
-    <row r="27" spans="2:11">
-      <c r="B27" s="1"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
-    </row>
-    <row r="28" spans="2:11">
-      <c r="B28" s="1"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7"/>
-      <c r="J28" s="7"/>
-      <c r="K28" s="7"/>
-    </row>
-    <row r="29" spans="2:11">
-      <c r="B29" s="1"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
-    </row>
-    <row r="30" spans="2:11">
-      <c r="B30" s="1"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
-      <c r="I30" s="7"/>
-      <c r="J30" s="7"/>
-      <c r="K30" s="7"/>
-    </row>
-    <row r="31" spans="2:11">
-      <c r="B31" s="1"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
-      <c r="J31" s="7"/>
-      <c r="K31" s="7"/>
-    </row>
-    <row r="32" spans="2:11">
-      <c r="B32" s="1"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
-      <c r="I32" s="7"/>
-      <c r="J32" s="7"/>
-      <c r="K32" s="7"/>
-    </row>
-    <row r="33" spans="2:11">
-      <c r="B33" s="1"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
-      <c r="I33" s="7"/>
-      <c r="J33" s="7"/>
-      <c r="K33" s="7"/>
-    </row>
-    <row r="34" spans="2:11">
-      <c r="B34" s="1"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="7"/>
-      <c r="I34" s="7"/>
-      <c r="J34" s="7"/>
-      <c r="K34" s="7"/>
-    </row>
-    <row r="35" spans="2:11">
-      <c r="B35" s="1"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
-      <c r="I35" s="7"/>
-      <c r="J35" s="7"/>
-      <c r="K35" s="7"/>
-    </row>
-    <row r="36" spans="2:11">
-      <c r="B36" s="1"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="7"/>
-      <c r="I36" s="7"/>
-      <c r="J36" s="7"/>
-      <c r="K36" s="7"/>
-    </row>
-    <row r="37" spans="2:11">
-      <c r="B37" s="1"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
-      <c r="I37" s="7"/>
-      <c r="J37" s="7"/>
-      <c r="K37" s="7"/>
-    </row>
-    <row r="38" spans="2:11">
-      <c r="B38" s="1"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="7"/>
-      <c r="H38" s="7"/>
-      <c r="I38" s="7"/>
-      <c r="J38" s="7"/>
-      <c r="K38" s="7"/>
-    </row>
-    <row r="39" spans="2:11">
-      <c r="B39" s="1"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
-      <c r="H39" s="7"/>
-      <c r="I39" s="7"/>
-      <c r="J39" s="7"/>
-      <c r="K39" s="7"/>
-    </row>
-    <row r="40" spans="2:11">
-      <c r="B40" s="1"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
-      <c r="H40" s="7"/>
-      <c r="I40" s="7"/>
-      <c r="J40" s="7"/>
-      <c r="K40" s="7"/>
-    </row>
-    <row r="41" spans="2:11">
-      <c r="B41" s="1"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="7"/>
-      <c r="H41" s="7"/>
-      <c r="I41" s="7"/>
-      <c r="J41" s="7"/>
-      <c r="K41" s="7"/>
-    </row>
-    <row r="42" spans="2:11">
-      <c r="B42" s="1"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7"/>
-      <c r="G42" s="7"/>
-      <c r="H42" s="7"/>
-      <c r="I42" s="7"/>
-      <c r="J42" s="7"/>
-      <c r="K42" s="7"/>
-    </row>
-    <row r="43" spans="2:11">
+      <c r="A16">
+        <v>2039</v>
+      </c>
+      <c r="B16" s="1">
+        <f>Summary_Removals!$H19</f>
+        <v>56346.525646373295</v>
+      </c>
+      <c r="C16" s="1">
+        <f>Summary_Removals!$H18</f>
+        <v>59531.643186932364</v>
+      </c>
+      <c r="D16" s="7">
+        <f>Summary_Removals!$H17</f>
+        <v>62997.934881515983</v>
+      </c>
+      <c r="E16" s="7">
+        <f>Summary_Removals!$H16</f>
+        <v>66847.083105281883</v>
+      </c>
+      <c r="F16" s="7">
+        <f>Summary_Removals!$H15</f>
+        <v>71262.303765193181</v>
+      </c>
+      <c r="G16" s="7">
+        <f>Summary_Removals!$H14</f>
+        <v>76580.791956977089</v>
+      </c>
+      <c r="H16" s="7">
+        <f>Summary_Removals!$H13</f>
+        <v>83431.293278018929</v>
+      </c>
+      <c r="I16" s="7">
+        <f>Summary_Removals!$H12</f>
+        <v>92995.858158672563</v>
+      </c>
+      <c r="J16" s="7">
+        <f>Summary_Removals!$H11</f>
+        <v>107509.4898329667</v>
+      </c>
+      <c r="K16" s="7">
+        <f>Summary_Removals!$H10</f>
+        <v>131219.23208679614</v>
+      </c>
+      <c r="L16" s="6">
+        <f t="shared" si="0"/>
+        <v>808722.15589872818</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17">
+        <v>2040</v>
+      </c>
+      <c r="B17" s="1">
+        <f>Summary_Removals!$H20</f>
+        <v>53384.232447029673</v>
+      </c>
+      <c r="C17" s="1">
+        <f>Summary_Removals!$H19</f>
+        <v>56346.525646373295</v>
+      </c>
+      <c r="D17" s="7">
+        <f>Summary_Removals!$H18</f>
+        <v>59531.643186932364</v>
+      </c>
+      <c r="E17" s="7">
+        <f>Summary_Removals!$H17</f>
+        <v>62997.934881515983</v>
+      </c>
+      <c r="F17" s="7">
+        <f>Summary_Removals!$H16</f>
+        <v>66847.083105281883</v>
+      </c>
+      <c r="G17" s="7">
+        <f>Summary_Removals!$H15</f>
+        <v>71262.303765193181</v>
+      </c>
+      <c r="H17" s="7">
+        <f>Summary_Removals!$H14</f>
+        <v>76580.791956977089</v>
+      </c>
+      <c r="I17" s="7">
+        <f>Summary_Removals!$H13</f>
+        <v>83431.293278018929</v>
+      </c>
+      <c r="J17" s="7">
+        <f>Summary_Removals!$H12</f>
+        <v>92995.858158672563</v>
+      </c>
+      <c r="K17" s="7">
+        <f>Summary_Removals!$H11</f>
+        <v>107509.4898329667</v>
+      </c>
+      <c r="L17" s="6">
+        <f t="shared" si="0"/>
+        <v>730887.15625896165</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18">
+        <v>2041</v>
+      </c>
+      <c r="B18" s="1">
+        <f>Summary_Removals!$H21</f>
+        <v>50609.580083052861</v>
+      </c>
+      <c r="C18" s="1">
+        <f>Summary_Removals!$H20</f>
+        <v>53384.232447029673</v>
+      </c>
+      <c r="D18" s="7">
+        <f>Summary_Removals!$H19</f>
+        <v>56346.525646373295</v>
+      </c>
+      <c r="E18" s="7">
+        <f>Summary_Removals!$H18</f>
+        <v>59531.643186932364</v>
+      </c>
+      <c r="F18" s="7">
+        <f>Summary_Removals!$H17</f>
+        <v>62997.934881515983</v>
+      </c>
+      <c r="G18" s="7">
+        <f>Summary_Removals!$H16</f>
+        <v>66847.083105281883</v>
+      </c>
+      <c r="H18" s="7">
+        <f>Summary_Removals!$H15</f>
+        <v>71262.303765193181</v>
+      </c>
+      <c r="I18" s="7">
+        <f>Summary_Removals!$H14</f>
+        <v>76580.791956977089</v>
+      </c>
+      <c r="J18" s="7">
+        <f>Summary_Removals!$H13</f>
+        <v>83431.293278018929</v>
+      </c>
+      <c r="K18" s="7">
+        <f>Summary_Removals!$H12</f>
+        <v>92995.858158672563</v>
+      </c>
+      <c r="L18" s="6">
+        <f t="shared" si="0"/>
+        <v>673987.24650904781</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19">
+        <v>2042</v>
+      </c>
+      <c r="B19" s="1">
+        <f>Summary_Removals!$H22</f>
+        <v>47999.892143159945</v>
+      </c>
+      <c r="C19" s="1">
+        <f>Summary_Removals!$H21</f>
+        <v>50609.580083052861</v>
+      </c>
+      <c r="D19" s="7">
+        <f>Summary_Removals!$H20</f>
+        <v>53384.232447029673</v>
+      </c>
+      <c r="E19" s="7">
+        <f>Summary_Removals!$H19</f>
+        <v>56346.525646373295</v>
+      </c>
+      <c r="F19" s="7">
+        <f>Summary_Removals!$H18</f>
+        <v>59531.643186932364</v>
+      </c>
+      <c r="G19" s="7">
+        <f>Summary_Removals!$H17</f>
+        <v>62997.934881515983</v>
+      </c>
+      <c r="H19" s="7">
+        <f>Summary_Removals!$H16</f>
+        <v>66847.083105281883</v>
+      </c>
+      <c r="I19" s="7">
+        <f>Summary_Removals!$H15</f>
+        <v>71262.303765193181</v>
+      </c>
+      <c r="J19" s="7">
+        <f>Summary_Removals!$H14</f>
+        <v>76580.791956977089</v>
+      </c>
+      <c r="K19" s="7">
+        <f>Summary_Removals!$H13</f>
+        <v>83431.293278018929</v>
+      </c>
+      <c r="L19" s="6">
+        <f t="shared" si="0"/>
+        <v>628991.28049353522</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20">
+        <v>2043</v>
+      </c>
+      <c r="B20" s="1">
+        <f>Summary_Removals!$H23</f>
+        <v>45539.35518525487</v>
+      </c>
+      <c r="C20" s="1">
+        <f>Summary_Removals!$H22</f>
+        <v>47999.892143159945</v>
+      </c>
+      <c r="D20" s="7">
+        <f>Summary_Removals!$H21</f>
+        <v>50609.580083052861</v>
+      </c>
+      <c r="E20" s="7">
+        <f>Summary_Removals!$H20</f>
+        <v>53384.232447029673</v>
+      </c>
+      <c r="F20" s="7">
+        <f>Summary_Removals!$H19</f>
+        <v>56346.525646373295</v>
+      </c>
+      <c r="G20" s="7">
+        <f>Summary_Removals!$H18</f>
+        <v>59531.643186932364</v>
+      </c>
+      <c r="H20" s="7">
+        <f>Summary_Removals!$H17</f>
+        <v>62997.934881515983</v>
+      </c>
+      <c r="I20" s="7">
+        <f>Summary_Removals!$H16</f>
+        <v>66847.083105281883</v>
+      </c>
+      <c r="J20" s="7">
+        <f>Summary_Removals!$H15</f>
+        <v>71262.303765193181</v>
+      </c>
+      <c r="K20" s="7">
+        <f>Summary_Removals!$H14</f>
+        <v>76580.791956977089</v>
+      </c>
+      <c r="L20" s="6">
+        <f t="shared" si="0"/>
+        <v>591099.3424007711</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21">
+        <v>2044</v>
+      </c>
+      <c r="B21" s="1">
+        <f>Summary_Removals!$H24</f>
+        <v>43216.02171730157</v>
+      </c>
+      <c r="C21" s="1">
+        <f>Summary_Removals!$H23</f>
+        <v>45539.35518525487</v>
+      </c>
+      <c r="D21" s="7">
+        <f>Summary_Removals!$H22</f>
+        <v>47999.892143159945</v>
+      </c>
+      <c r="E21" s="7">
+        <f>Summary_Removals!$H21</f>
+        <v>50609.580083052861</v>
+      </c>
+      <c r="F21" s="7">
+        <f>Summary_Removals!$H20</f>
+        <v>53384.232447029673</v>
+      </c>
+      <c r="G21" s="7">
+        <f>Summary_Removals!$H19</f>
+        <v>56346.525646373295</v>
+      </c>
+      <c r="H21" s="7">
+        <f>Summary_Removals!$H18</f>
+        <v>59531.643186932364</v>
+      </c>
+      <c r="I21" s="7">
+        <f>Summary_Removals!$H17</f>
+        <v>62997.934881515983</v>
+      </c>
+      <c r="J21" s="7">
+        <f>Summary_Removals!$H16</f>
+        <v>66847.083105281883</v>
+      </c>
+      <c r="K21" s="7">
+        <f>Summary_Removals!$H15</f>
+        <v>71262.303765193181</v>
+      </c>
+      <c r="L21" s="6">
+        <f t="shared" si="0"/>
+        <v>557734.57216109557</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22">
+        <v>2045</v>
+      </c>
+      <c r="B22" s="1">
+        <f>Summary_Removals!$H25</f>
+        <v>41020.21134229545</v>
+      </c>
+      <c r="C22" s="1">
+        <f>Summary_Removals!$H24</f>
+        <v>43216.02171730157</v>
+      </c>
+      <c r="D22" s="7">
+        <f>Summary_Removals!$H23</f>
+        <v>45539.35518525487</v>
+      </c>
+      <c r="E22" s="7">
+        <f>Summary_Removals!$H22</f>
+        <v>47999.892143159945</v>
+      </c>
+      <c r="F22" s="7">
+        <f>Summary_Removals!$H21</f>
+        <v>50609.580083052861</v>
+      </c>
+      <c r="G22" s="7">
+        <f>Summary_Removals!$H20</f>
+        <v>53384.232447029673</v>
+      </c>
+      <c r="H22" s="7">
+        <f>Summary_Removals!$H19</f>
+        <v>56346.525646373295</v>
+      </c>
+      <c r="I22" s="7">
+        <f>Summary_Removals!$H18</f>
+        <v>59531.643186932364</v>
+      </c>
+      <c r="J22" s="7">
+        <f>Summary_Removals!$H17</f>
+        <v>62997.934881515983</v>
+      </c>
+      <c r="K22" s="7">
+        <f>Summary_Removals!$H16</f>
+        <v>66847.083105281883</v>
+      </c>
+      <c r="L22" s="6">
+        <f t="shared" si="0"/>
+        <v>527492.47973819787</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23">
+        <v>2046</v>
+      </c>
+      <c r="B23" s="1">
+        <f>Summary_Removals!$H26</f>
+        <v>38943.651085778627</v>
+      </c>
+      <c r="C23" s="1">
+        <f>Summary_Removals!$H25</f>
+        <v>41020.21134229545</v>
+      </c>
+      <c r="D23" s="7">
+        <f>Summary_Removals!$H24</f>
+        <v>43216.02171730157</v>
+      </c>
+      <c r="E23" s="7">
+        <f>Summary_Removals!$H23</f>
+        <v>45539.35518525487</v>
+      </c>
+      <c r="F23" s="7">
+        <f>Summary_Removals!$H22</f>
+        <v>47999.892143159945</v>
+      </c>
+      <c r="G23" s="7">
+        <f>Summary_Removals!$H21</f>
+        <v>50609.580083052861</v>
+      </c>
+      <c r="H23" s="7">
+        <f>Summary_Removals!$H20</f>
+        <v>53384.232447029673</v>
+      </c>
+      <c r="I23" s="7">
+        <f>Summary_Removals!$H19</f>
+        <v>56346.525646373295</v>
+      </c>
+      <c r="J23" s="7">
+        <f>Summary_Removals!$H18</f>
+        <v>59531.643186932364</v>
+      </c>
+      <c r="K23" s="7">
+        <f>Summary_Removals!$H17</f>
+        <v>62997.934881515983</v>
+      </c>
+      <c r="L23" s="6">
+        <f t="shared" si="0"/>
+        <v>499589.04771869461</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24">
+        <v>2047</v>
+      </c>
+      <c r="B24" s="1">
+        <f>Summary_Removals!$H27</f>
+        <v>36979.00708357952</v>
+      </c>
+      <c r="C24" s="1">
+        <f>Summary_Removals!$H26</f>
+        <v>38943.651085778627</v>
+      </c>
+      <c r="D24" s="7">
+        <f>Summary_Removals!$H25</f>
+        <v>41020.21134229545</v>
+      </c>
+      <c r="E24" s="7">
+        <f>Summary_Removals!$H24</f>
+        <v>43216.02171730157</v>
+      </c>
+      <c r="F24" s="7">
+        <f>Summary_Removals!$H23</f>
+        <v>45539.35518525487</v>
+      </c>
+      <c r="G24" s="7">
+        <f>Summary_Removals!$H22</f>
+        <v>47999.892143159945</v>
+      </c>
+      <c r="H24" s="7">
+        <f>Summary_Removals!$H21</f>
+        <v>50609.580083052861</v>
+      </c>
+      <c r="I24" s="7">
+        <f>Summary_Removals!$H20</f>
+        <v>53384.232447029673</v>
+      </c>
+      <c r="J24" s="7">
+        <f>Summary_Removals!$H19</f>
+        <v>56346.525646373295</v>
+      </c>
+      <c r="K24" s="7">
+        <f>Summary_Removals!$H18</f>
+        <v>59531.643186932364</v>
+      </c>
+      <c r="L24" s="6">
+        <f t="shared" si="0"/>
+        <v>473570.11992075818</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25">
+        <v>2048</v>
+      </c>
+      <c r="B25" s="1">
+        <f>Summary_Removals!$H28</f>
+        <v>35119.623968787288</v>
+      </c>
+      <c r="C25" s="1">
+        <f>Summary_Removals!$H27</f>
+        <v>36979.00708357952</v>
+      </c>
+      <c r="D25" s="7">
+        <f>Summary_Removals!$H26</f>
+        <v>38943.651085778627</v>
+      </c>
+      <c r="E25" s="7">
+        <f>Summary_Removals!$H25</f>
+        <v>41020.21134229545</v>
+      </c>
+      <c r="F25" s="7">
+        <f>Summary_Removals!$H24</f>
+        <v>43216.02171730157</v>
+      </c>
+      <c r="G25" s="7">
+        <f>Summary_Removals!$H23</f>
+        <v>45539.35518525487</v>
+      </c>
+      <c r="H25" s="7">
+        <f>Summary_Removals!$H22</f>
+        <v>47999.892143159945</v>
+      </c>
+      <c r="I25" s="7">
+        <f>Summary_Removals!$H21</f>
+        <v>50609.580083052861</v>
+      </c>
+      <c r="J25" s="7">
+        <f>Summary_Removals!$H20</f>
+        <v>53384.232447029673</v>
+      </c>
+      <c r="K25" s="7">
+        <f>Summary_Removals!$H19</f>
+        <v>56346.525646373295</v>
+      </c>
+      <c r="L25" s="6">
+        <f t="shared" si="0"/>
+        <v>449158.10070261307</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26">
+        <v>2049</v>
+      </c>
+      <c r="B26" s="1">
+        <f>Summary_Removals!$H29</f>
+        <v>33359.374926236385</v>
+      </c>
+      <c r="C26" s="1">
+        <f>Summary_Removals!$H28</f>
+        <v>35119.623968787288</v>
+      </c>
+      <c r="D26" s="7">
+        <f>Summary_Removals!$H27</f>
+        <v>36979.00708357952</v>
+      </c>
+      <c r="E26" s="7">
+        <f>Summary_Removals!$H26</f>
+        <v>38943.651085778627</v>
+      </c>
+      <c r="F26" s="7">
+        <f>Summary_Removals!$H25</f>
+        <v>41020.21134229545</v>
+      </c>
+      <c r="G26" s="7">
+        <f>Summary_Removals!$H24</f>
+        <v>43216.02171730157</v>
+      </c>
+      <c r="H26" s="7">
+        <f>Summary_Removals!$H23</f>
+        <v>45539.35518525487</v>
+      </c>
+      <c r="I26" s="7">
+        <f>Summary_Removals!$H22</f>
+        <v>47999.892143159945</v>
+      </c>
+      <c r="J26" s="7">
+        <f>Summary_Removals!$H21</f>
+        <v>50609.580083052861</v>
+      </c>
+      <c r="K26" s="7">
+        <f>Summary_Removals!$H20</f>
+        <v>53384.232447029673</v>
+      </c>
+      <c r="L26" s="6">
+        <f t="shared" si="0"/>
+        <v>426170.94998247619</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27">
+        <v>2050</v>
+      </c>
+      <c r="B27" s="1">
+        <f>Summary_Removals!$H30</f>
+        <v>31692.571108202519</v>
+      </c>
+      <c r="C27" s="1">
+        <f>Summary_Removals!$H29</f>
+        <v>33359.374926236385</v>
+      </c>
+      <c r="D27" s="7">
+        <f>Summary_Removals!$H28</f>
+        <v>35119.623968787288</v>
+      </c>
+      <c r="E27" s="7">
+        <f>Summary_Removals!$H27</f>
+        <v>36979.00708357952</v>
+      </c>
+      <c r="F27" s="7">
+        <f>Summary_Removals!$H26</f>
+        <v>38943.651085778627</v>
+      </c>
+      <c r="G27" s="7">
+        <f>Summary_Removals!$H25</f>
+        <v>41020.21134229545</v>
+      </c>
+      <c r="H27" s="7">
+        <f>Summary_Removals!$H24</f>
+        <v>43216.02171730157</v>
+      </c>
+      <c r="I27" s="7">
+        <f>Summary_Removals!$H23</f>
+        <v>45539.35518525487</v>
+      </c>
+      <c r="J27" s="7">
+        <f>Summary_Removals!$H22</f>
+        <v>47999.892143159945</v>
+      </c>
+      <c r="K27" s="7">
+        <f>Summary_Removals!$H21</f>
+        <v>50609.580083052861</v>
+      </c>
+      <c r="L27" s="6">
+        <f t="shared" si="0"/>
+        <v>404479.28864364902</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28">
+        <v>2051</v>
+      </c>
+      <c r="B28" s="1">
+        <f>Summary_Removals!$H31</f>
+        <v>30113.903246855327</v>
+      </c>
+      <c r="C28" s="1">
+        <f>Summary_Removals!$H30</f>
+        <v>31692.571108202519</v>
+      </c>
+      <c r="D28" s="7">
+        <f>Summary_Removals!$H29</f>
+        <v>33359.374926236385</v>
+      </c>
+      <c r="E28" s="7">
+        <f>Summary_Removals!$H28</f>
+        <v>35119.623968787288</v>
+      </c>
+      <c r="F28" s="7">
+        <f>Summary_Removals!$H27</f>
+        <v>36979.00708357952</v>
+      </c>
+      <c r="G28" s="7">
+        <f>Summary_Removals!$H26</f>
+        <v>38943.651085778627</v>
+      </c>
+      <c r="H28" s="7">
+        <f>Summary_Removals!$H25</f>
+        <v>41020.21134229545</v>
+      </c>
+      <c r="I28" s="7">
+        <f>Summary_Removals!$H24</f>
+        <v>43216.02171730157</v>
+      </c>
+      <c r="J28" s="7">
+        <f>Summary_Removals!$H23</f>
+        <v>45539.35518525487</v>
+      </c>
+      <c r="K28" s="7">
+        <f>Summary_Removals!$H22</f>
+        <v>47999.892143159945</v>
+      </c>
+      <c r="L28" s="6">
+        <f t="shared" si="0"/>
+        <v>383983.61180745147</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29">
+        <v>2052</v>
+      </c>
+      <c r="B29" s="1">
+        <f>Summary_Removals!$H32</f>
+        <v>28618.401049714437</v>
+      </c>
+      <c r="C29" s="1">
+        <f>Summary_Removals!$H31</f>
+        <v>30113.903246855327</v>
+      </c>
+      <c r="D29" s="7">
+        <f>Summary_Removals!$H30</f>
+        <v>31692.571108202519</v>
+      </c>
+      <c r="E29" s="7">
+        <f>Summary_Removals!$H29</f>
+        <v>33359.374926236385</v>
+      </c>
+      <c r="F29" s="7">
+        <f>Summary_Removals!$H28</f>
+        <v>35119.623968787288</v>
+      </c>
+      <c r="G29" s="7">
+        <f>Summary_Removals!$H27</f>
+        <v>36979.00708357952</v>
+      </c>
+      <c r="H29" s="7">
+        <f>Summary_Removals!$H26</f>
+        <v>38943.651085778627</v>
+      </c>
+      <c r="I29" s="7">
+        <f>Summary_Removals!$H25</f>
+        <v>41020.21134229545</v>
+      </c>
+      <c r="J29" s="7">
+        <f>Summary_Removals!$H24</f>
+        <v>43216.02171730157</v>
+      </c>
+      <c r="K29" s="7">
+        <f>Summary_Removals!$H23</f>
+        <v>45539.35518525487</v>
+      </c>
+      <c r="L29" s="6">
+        <f t="shared" si="0"/>
+        <v>364602.12071400601</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30">
+        <v>2053</v>
+      </c>
+      <c r="B30" s="1">
+        <f>Summary_Removals!$H33</f>
+        <v>27201.402702210136</v>
+      </c>
+      <c r="C30" s="1">
+        <f>Summary_Removals!$H32</f>
+        <v>28618.401049714437</v>
+      </c>
+      <c r="D30" s="7">
+        <f>Summary_Removals!$H31</f>
+        <v>30113.903246855327</v>
+      </c>
+      <c r="E30" s="7">
+        <f>Summary_Removals!$H30</f>
+        <v>31692.571108202519</v>
+      </c>
+      <c r="F30" s="7">
+        <f>Summary_Removals!$H29</f>
+        <v>33359.374926236385</v>
+      </c>
+      <c r="G30" s="7">
+        <f>Summary_Removals!$H28</f>
+        <v>35119.623968787288</v>
+      </c>
+      <c r="H30" s="7">
+        <f>Summary_Removals!$H27</f>
+        <v>36979.00708357952</v>
+      </c>
+      <c r="I30" s="7">
+        <f>Summary_Removals!$H26</f>
+        <v>38943.651085778627</v>
+      </c>
+      <c r="J30" s="7">
+        <f>Summary_Removals!$H25</f>
+        <v>41020.21134229545</v>
+      </c>
+      <c r="K30" s="7">
+        <f>Summary_Removals!$H24</f>
+        <v>43216.02171730157</v>
+      </c>
+      <c r="L30" s="6">
+        <f t="shared" si="0"/>
+        <v>346264.16823096125</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="A31">
+        <v>2054</v>
+      </c>
+      <c r="B31" s="1">
+        <f>Summary_Removals!$H34</f>
+        <v>25858.53036485178</v>
+      </c>
+      <c r="C31" s="1">
+        <f>Summary_Removals!$H33</f>
+        <v>27201.402702210136</v>
+      </c>
+      <c r="D31" s="7">
+        <f>Summary_Removals!$H32</f>
+        <v>28618.401049714437</v>
+      </c>
+      <c r="E31" s="7">
+        <f>Summary_Removals!$H31</f>
+        <v>30113.903246855327</v>
+      </c>
+      <c r="F31" s="7">
+        <f>Summary_Removals!$H30</f>
+        <v>31692.571108202519</v>
+      </c>
+      <c r="G31" s="7">
+        <f>Summary_Removals!$H29</f>
+        <v>33359.374926236385</v>
+      </c>
+      <c r="H31" s="7">
+        <f>Summary_Removals!$H28</f>
+        <v>35119.623968787288</v>
+      </c>
+      <c r="I31" s="7">
+        <f>Summary_Removals!$H27</f>
+        <v>36979.00708357952</v>
+      </c>
+      <c r="J31" s="7">
+        <f>Summary_Removals!$H26</f>
+        <v>38943.651085778627</v>
+      </c>
+      <c r="K31" s="7">
+        <f>Summary_Removals!$H25</f>
+        <v>41020.21134229545</v>
+      </c>
+      <c r="L31" s="6">
+        <f t="shared" si="0"/>
+        <v>328906.67687851144</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32">
+        <v>2055</v>
+      </c>
+      <c r="B32" s="1">
+        <f>Summary_Removals!$H35</f>
+        <v>24585.669439431484</v>
+      </c>
+      <c r="C32" s="1">
+        <f>Summary_Removals!$H34</f>
+        <v>25858.53036485178</v>
+      </c>
+      <c r="D32" s="7">
+        <f>Summary_Removals!$H33</f>
+        <v>27201.402702210136</v>
+      </c>
+      <c r="E32" s="7">
+        <f>Summary_Removals!$H32</f>
+        <v>28618.401049714437</v>
+      </c>
+      <c r="F32" s="7">
+        <f>Summary_Removals!$H31</f>
+        <v>30113.903246855327</v>
+      </c>
+      <c r="G32" s="7">
+        <f>Summary_Removals!$H30</f>
+        <v>31692.571108202519</v>
+      </c>
+      <c r="H32" s="7">
+        <f>Summary_Removals!$H29</f>
+        <v>33359.374926236385</v>
+      </c>
+      <c r="I32" s="7">
+        <f>Summary_Removals!$H28</f>
+        <v>35119.623968787288</v>
+      </c>
+      <c r="J32" s="7">
+        <f>Summary_Removals!$H27</f>
+        <v>36979.00708357952</v>
+      </c>
+      <c r="K32" s="7">
+        <f>Summary_Removals!$H26</f>
+        <v>38943.651085778627</v>
+      </c>
+      <c r="L32" s="6">
+        <f t="shared" si="0"/>
+        <v>312472.13497564744</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
+      <c r="A33">
+        <v>2056</v>
+      </c>
+      <c r="B33" s="1">
+        <f>Summary_Removals!$H36</f>
+        <v>23378.950380107184</v>
+      </c>
+      <c r="C33" s="1">
+        <f>Summary_Removals!$H35</f>
+        <v>24585.669439431484</v>
+      </c>
+      <c r="D33" s="7">
+        <f>Summary_Removals!$H34</f>
+        <v>25858.53036485178</v>
+      </c>
+      <c r="E33" s="7">
+        <f>Summary_Removals!$H33</f>
+        <v>27201.402702210136</v>
+      </c>
+      <c r="F33" s="7">
+        <f>Summary_Removals!$H32</f>
+        <v>28618.401049714437</v>
+      </c>
+      <c r="G33" s="7">
+        <f>Summary_Removals!$H31</f>
+        <v>30113.903246855327</v>
+      </c>
+      <c r="H33" s="7">
+        <f>Summary_Removals!$H30</f>
+        <v>31692.571108202519</v>
+      </c>
+      <c r="I33" s="7">
+        <f>Summary_Removals!$H29</f>
+        <v>33359.374926236385</v>
+      </c>
+      <c r="J33" s="7">
+        <f>Summary_Removals!$H28</f>
+        <v>35119.623968787288</v>
+      </c>
+      <c r="K33" s="7">
+        <f>Summary_Removals!$H27</f>
+        <v>36979.00708357952</v>
+      </c>
+      <c r="L33" s="6">
+        <f t="shared" si="0"/>
+        <v>296907.43426997605</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34">
+        <v>2057</v>
+      </c>
+      <c r="B34" s="1">
+        <f>Summary_Removals!$H37</f>
+        <v>22234.732358414221</v>
+      </c>
+      <c r="C34" s="1">
+        <f>Summary_Removals!$H36</f>
+        <v>23378.950380107184</v>
+      </c>
+      <c r="D34" s="7">
+        <f>Summary_Removals!$H35</f>
+        <v>24585.669439431484</v>
+      </c>
+      <c r="E34" s="7">
+        <f>Summary_Removals!$H34</f>
+        <v>25858.53036485178</v>
+      </c>
+      <c r="F34" s="7">
+        <f>Summary_Removals!$H33</f>
+        <v>27201.402702210136</v>
+      </c>
+      <c r="G34" s="7">
+        <f>Summary_Removals!$H32</f>
+        <v>28618.401049714437</v>
+      </c>
+      <c r="H34" s="7">
+        <f>Summary_Removals!$H31</f>
+        <v>30113.903246855327</v>
+      </c>
+      <c r="I34" s="7">
+        <f>Summary_Removals!$H30</f>
+        <v>31692.571108202519</v>
+      </c>
+      <c r="J34" s="7">
+        <f>Summary_Removals!$H29</f>
+        <v>33359.374926236385</v>
+      </c>
+      <c r="K34" s="7">
+        <f>Summary_Removals!$H28</f>
+        <v>35119.623968787288</v>
+      </c>
+      <c r="L34" s="6">
+        <f t="shared" si="0"/>
+        <v>282163.15954481077</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35">
+        <v>2058</v>
+      </c>
+      <c r="B35" s="1">
+        <f>Summary_Removals!$H38</f>
+        <v>21149.588376887736</v>
+      </c>
+      <c r="C35" s="1">
+        <f>Summary_Removals!$H37</f>
+        <v>22234.732358414221</v>
+      </c>
+      <c r="D35" s="7">
+        <f>Summary_Removals!$H36</f>
+        <v>23378.950380107184</v>
+      </c>
+      <c r="E35" s="7">
+        <f>Summary_Removals!$H35</f>
+        <v>24585.669439431484</v>
+      </c>
+      <c r="F35" s="7">
+        <f>Summary_Removals!$H34</f>
+        <v>25858.53036485178</v>
+      </c>
+      <c r="G35" s="7">
+        <f>Summary_Removals!$H33</f>
+        <v>27201.402702210136</v>
+      </c>
+      <c r="H35" s="7">
+        <f>Summary_Removals!$H32</f>
+        <v>28618.401049714437</v>
+      </c>
+      <c r="I35" s="7">
+        <f>Summary_Removals!$H31</f>
+        <v>30113.903246855327</v>
+      </c>
+      <c r="J35" s="7">
+        <f>Summary_Removals!$H30</f>
+        <v>31692.571108202519</v>
+      </c>
+      <c r="K35" s="7">
+        <f>Summary_Removals!$H29</f>
+        <v>33359.374926236385</v>
+      </c>
+      <c r="L35" s="6">
+        <f t="shared" si="0"/>
+        <v>268193.12395291124</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
+      <c r="A36">
+        <v>2059</v>
+      </c>
+      <c r="B36" s="1">
+        <f>Summary_Removals!$H39</f>
+        <v>20120.291580568559</v>
+      </c>
+      <c r="C36" s="1">
+        <f>Summary_Removals!$H38</f>
+        <v>21149.588376887736</v>
+      </c>
+      <c r="D36" s="7">
+        <f>Summary_Removals!$H37</f>
+        <v>22234.732358414221</v>
+      </c>
+      <c r="E36" s="7">
+        <f>Summary_Removals!$H36</f>
+        <v>23378.950380107184</v>
+      </c>
+      <c r="F36" s="7">
+        <f>Summary_Removals!$H35</f>
+        <v>24585.669439431484</v>
+      </c>
+      <c r="G36" s="7">
+        <f>Summary_Removals!$H34</f>
+        <v>25858.53036485178</v>
+      </c>
+      <c r="H36" s="7">
+        <f>Summary_Removals!$H33</f>
+        <v>27201.402702210136</v>
+      </c>
+      <c r="I36" s="7">
+        <f>Summary_Removals!$H32</f>
+        <v>28618.401049714437</v>
+      </c>
+      <c r="J36" s="7">
+        <f>Summary_Removals!$H31</f>
+        <v>30113.903246855327</v>
+      </c>
+      <c r="K36" s="7">
+        <f>Summary_Removals!$H30</f>
+        <v>31692.571108202519</v>
+      </c>
+      <c r="L36" s="6">
+        <f t="shared" si="0"/>
+        <v>254954.04060724337</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="A37">
+        <v>2060</v>
+      </c>
+      <c r="B37" s="1">
+        <f>Summary_Removals!$H40</f>
+        <v>19143.802600336494</v>
+      </c>
+      <c r="C37" s="1">
+        <f>Summary_Removals!$H39</f>
+        <v>20120.291580568559</v>
+      </c>
+      <c r="D37" s="7">
+        <f>Summary_Removals!$H38</f>
+        <v>21149.588376887736</v>
+      </c>
+      <c r="E37" s="7">
+        <f>Summary_Removals!$H37</f>
+        <v>22234.732358414221</v>
+      </c>
+      <c r="F37" s="7">
+        <f>Summary_Removals!$H36</f>
+        <v>23378.950380107184</v>
+      </c>
+      <c r="G37" s="7">
+        <f>Summary_Removals!$H35</f>
+        <v>24585.669439431484</v>
+      </c>
+      <c r="H37" s="7">
+        <f>Summary_Removals!$H34</f>
+        <v>25858.53036485178</v>
+      </c>
+      <c r="I37" s="7">
+        <f>Summary_Removals!$H33</f>
+        <v>27201.402702210136</v>
+      </c>
+      <c r="J37" s="7">
+        <f>Summary_Removals!$H32</f>
+        <v>28618.401049714437</v>
+      </c>
+      <c r="K37" s="7">
+        <f>Summary_Removals!$H31</f>
+        <v>30113.903246855327</v>
+      </c>
+      <c r="L37" s="6">
+        <f t="shared" si="0"/>
+        <v>242405.27209937741</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12">
+      <c r="A38">
+        <v>2061</v>
+      </c>
+      <c r="B38" s="1">
+        <f>Summary_Removals!$H41</f>
+        <v>18217.25780993624</v>
+      </c>
+      <c r="C38" s="1">
+        <f>Summary_Removals!$H40</f>
+        <v>19143.802600336494</v>
+      </c>
+      <c r="D38" s="7">
+        <f>Summary_Removals!$H39</f>
+        <v>20120.291580568559</v>
+      </c>
+      <c r="E38" s="7">
+        <f>Summary_Removals!$H38</f>
+        <v>21149.588376887736</v>
+      </c>
+      <c r="F38" s="7">
+        <f>Summary_Removals!$H37</f>
+        <v>22234.732358414221</v>
+      </c>
+      <c r="G38" s="7">
+        <f>Summary_Removals!$H36</f>
+        <v>23378.950380107184</v>
+      </c>
+      <c r="H38" s="7">
+        <f>Summary_Removals!$H35</f>
+        <v>24585.669439431484</v>
+      </c>
+      <c r="I38" s="7">
+        <f>Summary_Removals!$H34</f>
+        <v>25858.53036485178</v>
+      </c>
+      <c r="J38" s="7">
+        <f>Summary_Removals!$H33</f>
+        <v>27201.402702210136</v>
+      </c>
+      <c r="K38" s="7">
+        <f>Summary_Removals!$H32</f>
+        <v>28618.401049714437</v>
+      </c>
+      <c r="L38" s="6">
+        <f t="shared" si="0"/>
+        <v>230508.62666245832</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
+      <c r="A39">
+        <v>2062</v>
+      </c>
+      <c r="B39" s="1">
+        <f>Summary_Removals!$H42</f>
+        <v>17337.958406313352</v>
+      </c>
+      <c r="C39" s="1">
+        <f>Summary_Removals!$H41</f>
+        <v>18217.25780993624</v>
+      </c>
+      <c r="D39" s="7">
+        <f>Summary_Removals!$H40</f>
+        <v>19143.802600336494</v>
+      </c>
+      <c r="E39" s="7">
+        <f>Summary_Removals!$H39</f>
+        <v>20120.291580568559</v>
+      </c>
+      <c r="F39" s="7">
+        <f>Summary_Removals!$H38</f>
+        <v>21149.588376887736</v>
+      </c>
+      <c r="G39" s="7">
+        <f>Summary_Removals!$H37</f>
+        <v>22234.732358414221</v>
+      </c>
+      <c r="H39" s="7">
+        <f>Summary_Removals!$H36</f>
+        <v>23378.950380107184</v>
+      </c>
+      <c r="I39" s="7">
+        <f>Summary_Removals!$H35</f>
+        <v>24585.669439431484</v>
+      </c>
+      <c r="J39" s="7">
+        <f>Summary_Removals!$H34</f>
+        <v>25858.53036485178</v>
+      </c>
+      <c r="K39" s="7">
+        <f>Summary_Removals!$H33</f>
+        <v>27201.402702210136</v>
+      </c>
+      <c r="L39" s="6">
+        <f t="shared" si="0"/>
+        <v>219228.1840190572</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
+      <c r="A40">
+        <v>2063</v>
+      </c>
+      <c r="B40" s="1">
+        <f>Summary_Removals!$H43</f>
+        <v>16503.360240031056</v>
+      </c>
+      <c r="C40" s="1">
+        <f>Summary_Removals!$H42</f>
+        <v>17337.958406313352</v>
+      </c>
+      <c r="D40" s="7">
+        <f>Summary_Removals!$H41</f>
+        <v>18217.25780993624</v>
+      </c>
+      <c r="E40" s="7">
+        <f>Summary_Removals!$H40</f>
+        <v>19143.802600336494</v>
+      </c>
+      <c r="F40" s="7">
+        <f>Summary_Removals!$H39</f>
+        <v>20120.291580568559</v>
+      </c>
+      <c r="G40" s="7">
+        <f>Summary_Removals!$H38</f>
+        <v>21149.588376887736</v>
+      </c>
+      <c r="H40" s="7">
+        <f>Summary_Removals!$H37</f>
+        <v>22234.732358414221</v>
+      </c>
+      <c r="I40" s="7">
+        <f>Summary_Removals!$H36</f>
+        <v>23378.950380107184</v>
+      </c>
+      <c r="J40" s="7">
+        <f>Summary_Removals!$H35</f>
+        <v>24585.669439431484</v>
+      </c>
+      <c r="K40" s="7">
+        <f>Summary_Removals!$H34</f>
+        <v>25858.53036485178</v>
+      </c>
+      <c r="L40" s="6">
+        <f t="shared" si="0"/>
+        <v>208530.14155687811</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
+      <c r="A41">
+        <v>2064</v>
+      </c>
+      <c r="B41" s="1">
+        <f>Summary_Removals!$H44</f>
+        <v>15711.0643337696</v>
+      </c>
+      <c r="C41" s="1">
+        <f>Summary_Removals!$H43</f>
+        <v>16503.360240031056</v>
+      </c>
+      <c r="D41" s="7">
+        <f>Summary_Removals!$H42</f>
+        <v>17337.958406313352</v>
+      </c>
+      <c r="E41" s="7">
+        <f>Summary_Removals!$H41</f>
+        <v>18217.25780993624</v>
+      </c>
+      <c r="F41" s="7">
+        <f>Summary_Removals!$H40</f>
+        <v>19143.802600336494</v>
+      </c>
+      <c r="G41" s="7">
+        <f>Summary_Removals!$H39</f>
+        <v>20120.291580568559</v>
+      </c>
+      <c r="H41" s="7">
+        <f>Summary_Removals!$H38</f>
+        <v>21149.588376887736</v>
+      </c>
+      <c r="I41" s="7">
+        <f>Summary_Removals!$H37</f>
+        <v>22234.732358414221</v>
+      </c>
+      <c r="J41" s="7">
+        <f>Summary_Removals!$H36</f>
+        <v>23378.950380107184</v>
+      </c>
+      <c r="K41" s="7">
+        <f>Summary_Removals!$H35</f>
+        <v>24585.669439431484</v>
+      </c>
+      <c r="L41" s="6">
+        <f t="shared" si="0"/>
+        <v>198382.67552579593</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
+      <c r="A42">
+        <v>2065</v>
+      </c>
+      <c r="B42" s="1">
+        <f>Summary_Removals!$H45</f>
+        <v>14958.80803464601</v>
+      </c>
+      <c r="C42" s="1">
+        <f>Summary_Removals!$H44</f>
+        <v>15711.0643337696</v>
+      </c>
+      <c r="D42" s="7">
+        <f>Summary_Removals!$H43</f>
+        <v>16503.360240031056</v>
+      </c>
+      <c r="E42" s="7">
+        <f>Summary_Removals!$H42</f>
+        <v>17337.958406313352</v>
+      </c>
+      <c r="F42" s="7">
+        <f>Summary_Removals!$H41</f>
+        <v>18217.25780993624</v>
+      </c>
+      <c r="G42" s="7">
+        <f>Summary_Removals!$H40</f>
+        <v>19143.802600336494</v>
+      </c>
+      <c r="H42" s="7">
+        <f>Summary_Removals!$H39</f>
+        <v>20120.291580568559</v>
+      </c>
+      <c r="I42" s="7">
+        <f>Summary_Removals!$H38</f>
+        <v>21149.588376887736</v>
+      </c>
+      <c r="J42" s="7">
+        <f>Summary_Removals!$H37</f>
+        <v>22234.732358414221</v>
+      </c>
+      <c r="K42" s="7">
+        <f>Summary_Removals!$H36</f>
+        <v>23378.950380107184</v>
+      </c>
+      <c r="L42" s="6">
+        <f t="shared" si="0"/>
+        <v>188755.81412101045</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
+      <c r="B43" s="1">
+        <f>Summary_Removals!$H46</f>
+        <v>0</v>
+      </c>
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
@@ -11238,8 +12744,7 @@
       <c r="J43" s="7"/>
       <c r="K43" s="7"/>
     </row>
-    <row r="44" spans="2:11">
-      <c r="B44" s="6"/>
+    <row r="44" spans="1:12">
       <c r="D44" s="7"/>
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
@@ -11247,18 +12752,30 @@
       <c r="H44" s="7"/>
       <c r="I44" s="7"/>
       <c r="J44" s="7"/>
-      <c r="K44" s="7"/>
-    </row>
-    <row r="45" spans="2:11">
+      <c r="K44" t="s">
+        <v>38</v>
+      </c>
+      <c r="L44" s="1">
+        <f>SUM(B3:K42)</f>
+        <v>30332151.033396032</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12">
       <c r="E45" s="7"/>
       <c r="F45" s="7"/>
       <c r="G45" s="7"/>
       <c r="H45" s="7"/>
       <c r="I45" s="7"/>
       <c r="J45" s="7"/>
-      <c r="K45" s="7"/>
-    </row>
-    <row r="46" spans="2:11">
+      <c r="K45" t="s">
+        <v>39</v>
+      </c>
+      <c r="L45" s="1">
+        <f>L44/40</f>
+        <v>758303.77583490079</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12">
       <c r="F46" s="7"/>
       <c r="G46" s="7"/>
       <c r="H46" s="7"/>
@@ -11266,18 +12783,30 @@
       <c r="J46" s="7"/>
       <c r="K46" s="7"/>
     </row>
-    <row r="47" spans="2:11">
+    <row r="47" spans="1:12">
       <c r="G47" s="7"/>
       <c r="H47" s="7"/>
       <c r="I47" s="7"/>
       <c r="J47" s="7"/>
-      <c r="K47" s="7"/>
-    </row>
-    <row r="48" spans="2:11">
+      <c r="K47" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L47" s="6">
+        <f>SUM(L3:L12)</f>
+        <v>15965942.702463739</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12">
       <c r="H48" s="7"/>
       <c r="I48" s="7"/>
       <c r="J48" s="7"/>
-      <c r="K48" s="7"/>
+      <c r="K48" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="L48" s="6">
+        <f>L47/10</f>
+        <v>1596594.270246374</v>
+      </c>
     </row>
     <row r="49" spans="9:11">
       <c r="I49" s="7"/>

--- a/Mid_Estimate/ER_Summary.xlsx
+++ b/Mid_Estimate/ER_Summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mihirbendre/Documents/Gazelle/Gazelle_2026/Kenya_Project/Agricentric_SOC_Modeling/Mid_Estimate/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D247D3F7-C2E3-4A46-AF88-127165FADBB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CFA2A9E-7A76-464C-98D4-C4E79D062D0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" activeTab="3" xr2:uid="{72AD1D35-862B-EB40-AF7A-21135E5EFD45}"/>
+    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" activeTab="1" xr2:uid="{72AD1D35-862B-EB40-AF7A-21135E5EFD45}"/>
   </bookViews>
   <sheets>
     <sheet name="Net_Summary" sheetId="9" r:id="rId1"/>
@@ -9639,6 +9639,12 @@
         <v>77761.44093950266</v>
       </c>
     </row>
+    <row r="49" spans="7:8">
+      <c r="H49" s="1">
+        <f>H48/35000</f>
+        <v>2.2217554554143617</v>
+      </c>
+    </row>
     <row r="50" spans="7:8">
       <c r="G50" s="1" t="s">
         <v>24</v>
